--- a/test-output/NFRS_Test_Output.xlsx
+++ b/test-output/NFRS_Test_Output.xlsx
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="647">
   <si>
     <t>BS Year</t>
   </si>
@@ -363,7 +363,7 @@
     <t>Company Name</t>
   </si>
   <si>
-    <t>Himalayan Trading Pvt. Ltd.</t>
+    <t>ABC PRIVATE LIMITED</t>
   </si>
   <si>
     <t>Fiscal Year</t>
@@ -372,27 +372,15 @@
     <t>End Date BS</t>
   </si>
   <si>
-    <t>2082-03-31</t>
-  </si>
-  <si>
     <t>End Date AD</t>
   </si>
   <si>
-    <t>2025-07-16</t>
-  </si>
-  <si>
     <t>Start Date BS</t>
   </si>
   <si>
-    <t>2081-04-01</t>
-  </si>
-  <si>
     <t>Start Date AD</t>
   </si>
   <si>
-    <t>2024-07-17</t>
-  </si>
-  <si>
     <t>Rounding Level (NPR)</t>
   </si>
   <si>
@@ -405,13 +393,13 @@
     <t>PAN/VAT Number</t>
   </si>
   <si>
-    <t>301234567</t>
+    <t>123456789</t>
   </si>
   <si>
     <t>Registration No.</t>
   </si>
   <si>
-    <t>158/070/071</t>
+    <t>12345/074/075</t>
   </si>
   <si>
     <t>▶ Validation Dashboard</t>
@@ -513,552 +501,918 @@
     <t>Chairperson</t>
   </si>
   <si>
+    <t>Mr. A</t>
+  </si>
+  <si>
+    <t>Director</t>
+  </si>
+  <si>
+    <t>Mr. B</t>
+  </si>
+  <si>
+    <t>Accounts Head</t>
+  </si>
+  <si>
+    <t>Mr. C</t>
+  </si>
+  <si>
+    <t>Auditor Name</t>
+  </si>
+  <si>
+    <t>CA. A</t>
+  </si>
+  <si>
+    <t>Audit Firm</t>
+  </si>
+  <si>
+    <t>A &amp; Associates</t>
+  </si>
+  <si>
+    <t>Account Name</t>
+  </si>
+  <si>
+    <t>NFRS Category</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>Opening Dr</t>
+  </si>
+  <si>
+    <t>Opening Cr</t>
+  </si>
+  <si>
+    <t>During Dr</t>
+  </si>
+  <si>
+    <t>During Cr</t>
+  </si>
+  <si>
+    <t>Adj Dr</t>
+  </si>
+  <si>
+    <t>Adj Cr</t>
+  </si>
+  <si>
+    <t>Closing Dr</t>
+  </si>
+  <si>
+    <t>Closing Cr</t>
+  </si>
+  <si>
+    <t>Net Balance</t>
+  </si>
+  <si>
+    <t>Paid-up Capital</t>
+  </si>
+  <si>
+    <t>share_capital</t>
+  </si>
+  <si>
+    <t>Reserves &amp; Surplus</t>
+  </si>
+  <si>
+    <t>general_reserve</t>
+  </si>
+  <si>
+    <t>General Reserve</t>
+  </si>
+  <si>
+    <t>Bank A</t>
+  </si>
+  <si>
+    <t>bank_current_account</t>
+  </si>
+  <si>
+    <t>Bank Balance</t>
+  </si>
+  <si>
+    <t>Bank B</t>
+  </si>
+  <si>
+    <t>Creditor A</t>
+  </si>
+  <si>
+    <t>trade_payables_creditors</t>
+  </si>
+  <si>
+    <t>Sundry Creditors</t>
+  </si>
+  <si>
+    <t>Creditor B</t>
+  </si>
+  <si>
+    <t>Creditor C</t>
+  </si>
+  <si>
+    <t>Audit Fee Payable</t>
+  </si>
+  <si>
+    <t>audit_fee_payable</t>
+  </si>
+  <si>
+    <t>Staff Bonus Payable</t>
+  </si>
+  <si>
+    <t>employee_payables_bonus</t>
+  </si>
+  <si>
+    <t>Provision for CSR</t>
+  </si>
+  <si>
+    <t>provisions_current</t>
+  </si>
+  <si>
+    <t>Director A</t>
+  </si>
+  <si>
+    <t>unclassified</t>
+  </si>
+  <si>
+    <t>Director B</t>
+  </si>
+  <si>
+    <t>Employee A</t>
+  </si>
+  <si>
+    <t>employee_payables_salary</t>
+  </si>
+  <si>
+    <t>Salary Payable</t>
+  </si>
+  <si>
+    <t>Employee B</t>
+  </si>
+  <si>
+    <t>Provident Fund Payable</t>
+  </si>
+  <si>
+    <t>employee_payables_pf</t>
+  </si>
+  <si>
+    <t>TDS - Audit Fee</t>
+  </si>
+  <si>
+    <t>tds_payable</t>
+  </si>
+  <si>
+    <t>TDS Payable</t>
+  </si>
+  <si>
+    <t>TDS - Ltd. Company</t>
+  </si>
+  <si>
+    <t>TDS- Proprietorship</t>
+  </si>
+  <si>
+    <t>TDS - Pvt. Ltd</t>
+  </si>
+  <si>
+    <t>TDS- Salary</t>
+  </si>
+  <si>
+    <t>TDS - SST</t>
+  </si>
+  <si>
+    <t>TDS - Rental</t>
+  </si>
+  <si>
+    <t>VAT</t>
+  </si>
+  <si>
+    <t>other_payables</t>
+  </si>
+  <si>
+    <t>VAT Payable</t>
+  </si>
+  <si>
+    <t>Income Tax Payable</t>
+  </si>
+  <si>
+    <t>income_tax_payable</t>
+  </si>
+  <si>
+    <t>Land</t>
+  </si>
+  <si>
+    <t>ppe_land</t>
+  </si>
+  <si>
+    <t>Building</t>
+  </si>
+  <si>
+    <t>ppe_buildings</t>
+  </si>
+  <si>
+    <t>Buildings</t>
+  </si>
+  <si>
+    <t>Furniture &amp; Office Equipment</t>
+  </si>
+  <si>
+    <t>ppe_furniture</t>
+  </si>
+  <si>
+    <t>Furniture &amp; Fixtures</t>
+  </si>
+  <si>
+    <t>Vehicle</t>
+  </si>
+  <si>
+    <t>ppe_vehicles</t>
+  </si>
+  <si>
+    <t>Vehicles</t>
+  </si>
+  <si>
+    <t>Plant &amp; Machinery</t>
+  </si>
+  <si>
+    <t>ppe_plant_machinery</t>
+  </si>
+  <si>
+    <t>Tally Software</t>
+  </si>
+  <si>
+    <t>ppe_intangibles</t>
+  </si>
+  <si>
+    <t>Intangible Assets</t>
+  </si>
+  <si>
+    <t>Leasehold</t>
+  </si>
+  <si>
+    <t>Work In Progress</t>
+  </si>
+  <si>
+    <t>inventory_wip</t>
+  </si>
+  <si>
+    <t>Work in Progress</t>
+  </si>
+  <si>
+    <t>Biological Assets</t>
+  </si>
+  <si>
+    <t>nca_other</t>
+  </si>
+  <si>
+    <t>Accumulated Depreciation</t>
+  </si>
+  <si>
+    <t>accum_depreciation</t>
+  </si>
+  <si>
+    <t>Shares of XYZ Ltd.</t>
+  </si>
+  <si>
+    <t>investment_listed_trading</t>
+  </si>
+  <si>
+    <t>Investment in Listed Shares</t>
+  </si>
+  <si>
+    <t>Shares of PQR Ltd.</t>
+  </si>
+  <si>
+    <t>investment_unlisted</t>
+  </si>
+  <si>
+    <t>Investment in Unlisted Shares</t>
+  </si>
+  <si>
+    <t>Provision for Impairment on Investment</t>
+  </si>
+  <si>
+    <t>provision_impairment_investment</t>
+  </si>
+  <si>
+    <t>Deposits</t>
+  </si>
+  <si>
+    <t>nca_deposits</t>
+  </si>
+  <si>
+    <t>Deposits (Non-Current)</t>
+  </si>
+  <si>
+    <t>Loans &amp; Advances (Asset)</t>
+  </si>
+  <si>
+    <t>other_receivables_loans</t>
+  </si>
+  <si>
+    <t>Loans &amp; Advances (Current)</t>
+  </si>
+  <si>
+    <t>Staff Advance</t>
+  </si>
+  <si>
+    <t>other_receivables_staff_advance</t>
+  </si>
+  <si>
+    <t>Debtor A</t>
+  </si>
+  <si>
+    <t>trade_receivables</t>
+  </si>
+  <si>
+    <t>Sundry Debtors</t>
+  </si>
+  <si>
+    <t>Debtor B</t>
+  </si>
+  <si>
+    <t>Debtor C</t>
+  </si>
+  <si>
+    <t>Provision for Impairment on debtors</t>
+  </si>
+  <si>
+    <t>provision_impairment_debtors</t>
+  </si>
+  <si>
+    <t>Provision for Impairment on Debtors</t>
+  </si>
+  <si>
+    <t>Director C</t>
+  </si>
+  <si>
+    <t>Director D</t>
+  </si>
+  <si>
+    <t>Petty Cash</t>
+  </si>
+  <si>
+    <t>cash_in_hand</t>
+  </si>
+  <si>
+    <t>Cash in Hand</t>
+  </si>
+  <si>
+    <t>Bank C</t>
+  </si>
+  <si>
+    <t>Bank D</t>
+  </si>
+  <si>
+    <t>Inventory</t>
+  </si>
+  <si>
+    <t>inventory_finished_goods</t>
+  </si>
+  <si>
+    <t>Finished Goods</t>
+  </si>
+  <si>
+    <t>Advance Tax</t>
+  </si>
+  <si>
+    <t>other_receivables_tds</t>
+  </si>
+  <si>
+    <t>TDS Receivable</t>
+  </si>
+  <si>
+    <t>Non Current Assets held for Sale</t>
+  </si>
+  <si>
+    <t>other_receivables_other</t>
+  </si>
+  <si>
+    <t>Non-Current Assets Held for Sale</t>
+  </si>
+  <si>
+    <t>Sales Revenue</t>
+  </si>
+  <si>
+    <t>revenue_sales</t>
+  </si>
+  <si>
+    <t>Service Income</t>
+  </si>
+  <si>
+    <t>revenue_services</t>
+  </si>
+  <si>
+    <t>Purchase</t>
+  </si>
+  <si>
+    <t>cogs_purchases</t>
+  </si>
+  <si>
+    <t>Purchases</t>
+  </si>
+  <si>
+    <t>Wages</t>
+  </si>
+  <si>
+    <t>direct_wages</t>
+  </si>
+  <si>
+    <t>Direct Wages</t>
+  </si>
+  <si>
+    <t>Other Direct Expenses</t>
+  </si>
+  <si>
+    <t>direct_expenses_other</t>
+  </si>
+  <si>
+    <t>Direct Expenses</t>
+  </si>
+  <si>
+    <t>Interest Income</t>
+  </si>
+  <si>
+    <t>other_income_interest</t>
+  </si>
+  <si>
+    <t>Commission Income</t>
+  </si>
+  <si>
+    <t>other_income_misc</t>
+  </si>
+  <si>
+    <t>Other Indirect Income</t>
+  </si>
+  <si>
+    <t>Other Income</t>
+  </si>
+  <si>
+    <t>Rental Income</t>
+  </si>
+  <si>
+    <t>other_income_rental</t>
+  </si>
+  <si>
+    <t>Dividend Income</t>
+  </si>
+  <si>
+    <t>other_income_dividend</t>
+  </si>
+  <si>
+    <t>Salaries &amp; Wages</t>
+  </si>
+  <si>
+    <t>emp_expense_salaries</t>
+  </si>
+  <si>
+    <t>Salaries</t>
+  </si>
+  <si>
+    <t>Allowances</t>
+  </si>
+  <si>
+    <t>emp_expense_welfare</t>
+  </si>
+  <si>
+    <t>Staff Welfare</t>
+  </si>
+  <si>
+    <t>PF / SSF / CIT</t>
+  </si>
+  <si>
+    <t>emp_expense_pf</t>
+  </si>
+  <si>
+    <t>Provident Fund Expense</t>
+  </si>
+  <si>
+    <t>Staff Bonus</t>
+  </si>
+  <si>
+    <t>emp_expense_bonus</t>
+  </si>
+  <si>
+    <t>Leave Encashment</t>
+  </si>
+  <si>
+    <t>Other employee related expenses</t>
+  </si>
+  <si>
+    <t>Interest expense</t>
+  </si>
+  <si>
+    <t>finance_cost_interest</t>
+  </si>
+  <si>
+    <t>Interest Expense</t>
+  </si>
+  <si>
+    <t>Bank Charges</t>
+  </si>
+  <si>
+    <t>finance_cost_bank_charges</t>
+  </si>
+  <si>
+    <t>depreciation_expense</t>
+  </si>
+  <si>
+    <t>Depreciation Expense</t>
+  </si>
+  <si>
+    <t>Impairment on Receivables</t>
+  </si>
+  <si>
+    <t>impairment_expense</t>
+  </si>
+  <si>
+    <t>Impairment Expense</t>
+  </si>
+  <si>
+    <t>Impairment on Unlisted Shares</t>
+  </si>
+  <si>
+    <t>Pool A</t>
+  </si>
+  <si>
+    <t>admin_repairs</t>
+  </si>
+  <si>
+    <t>Repairs &amp; Maintenance</t>
+  </si>
+  <si>
+    <t>Pool B</t>
+  </si>
+  <si>
+    <t>Pool C</t>
+  </si>
+  <si>
+    <t>Pool D</t>
+  </si>
+  <si>
+    <t>Pool E</t>
+  </si>
+  <si>
+    <t>Income Tax Expense</t>
+  </si>
+  <si>
+    <t>income_tax_expense</t>
+  </si>
+  <si>
+    <t>Audit Fee</t>
+  </si>
+  <si>
+    <t>admin_audit_fee</t>
+  </si>
+  <si>
+    <t>Advertisement &amp; Business Promotion</t>
+  </si>
+  <si>
+    <t>admin_other</t>
+  </si>
+  <si>
+    <t>Advertisement &amp; Promotion</t>
+  </si>
+  <si>
+    <t>Fuel Expenses</t>
+  </si>
+  <si>
+    <t>admin_traveling</t>
+  </si>
+  <si>
+    <t>Traveling &amp; Conveyance</t>
+  </si>
+  <si>
+    <t>House Rent</t>
+  </si>
+  <si>
+    <t>admin_rent</t>
+  </si>
+  <si>
+    <t>Rent</t>
+  </si>
+  <si>
+    <t>Insurance Premium</t>
+  </si>
+  <si>
+    <t>admin_insurance</t>
+  </si>
+  <si>
+    <t>Insurance</t>
+  </si>
+  <si>
+    <t>Miscellaneous expenses</t>
+  </si>
+  <si>
+    <t>Miscellaneous Expenses</t>
+  </si>
+  <si>
+    <t>Printing &amp; Stationery</t>
+  </si>
+  <si>
+    <t>admin_printing</t>
+  </si>
+  <si>
+    <t>Refreshment Expenses</t>
+  </si>
+  <si>
+    <t>Travelling</t>
+  </si>
+  <si>
+    <t>Water &amp; Electricity Charges</t>
+  </si>
+  <si>
+    <t>admin_electricity</t>
+  </si>
+  <si>
+    <t>Electricity &amp; Water</t>
+  </si>
+  <si>
+    <t>Cash Credit</t>
+  </si>
+  <si>
+    <t>borrowings_current_cc</t>
+  </si>
+  <si>
+    <t>Working Capital Loan</t>
+  </si>
+  <si>
+    <t>borrowings_current_wc</t>
+  </si>
+  <si>
+    <t>STATEMENT OF FINANCIAL POSITION</t>
+  </si>
+  <si>
+    <t>As at 31 Ashadh 82 (15 July 2025)</t>
+  </si>
+  <si>
+    <t>All amounts in NPR (Nepalese Rupees)</t>
+  </si>
+  <si>
+    <t>Particulars</t>
+  </si>
+  <si>
+    <t>31 Ashadh 82</t>
+  </si>
+  <si>
+    <t>A.  NON-CURRENT ASSETS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Property, Plant and Equipment</t>
+  </si>
+  <si>
+    <t>3.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Investments</t>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Other Receivables (Non-current)</t>
+  </si>
+  <si>
+    <t>3.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Other Non-Current Assets</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>Total Non-Current Assets</t>
+  </si>
+  <si>
+    <t>B.  CURRENT ASSETS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Investments (Current)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Inventories</t>
+  </si>
+  <si>
+    <t>3.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Trade and Other Receivables</t>
+  </si>
+  <si>
+    <t>3.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Cash and Cash Equivalents</t>
+  </si>
+  <si>
+    <t>3.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Other Current Assets</t>
+  </si>
+  <si>
+    <t>3.6</t>
+  </si>
+  <si>
+    <t>Total Current Assets</t>
+  </si>
+  <si>
+    <t>TOTAL ASSETS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Share Capital</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Reserves</t>
+  </si>
+  <si>
+    <t>3.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Retained Earnings</t>
+  </si>
+  <si>
+    <t>Total Equity</t>
+  </si>
+  <si>
+    <t>D.  NON-CURRENT LIABILITIES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Loans and Borrowings</t>
+  </si>
+  <si>
+    <t>3.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Employee Benefit Liabilities</t>
+  </si>
+  <si>
+    <t>3.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Provisions</t>
+  </si>
+  <si>
+    <t>Total Non-Current Liabilities</t>
+  </si>
+  <si>
+    <t>E.  CURRENT LIABILITIES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Trade and Other Payables</t>
+  </si>
+  <si>
+    <t>3.13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Income Tax Liability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Employee Benefit Liability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Other Current Liabilities</t>
+  </si>
+  <si>
+    <t>Total Current Liabilities</t>
+  </si>
+  <si>
+    <t>TOTAL EQUITY AND LIABILITIES</t>
+  </si>
+  <si>
+    <t>Balance Check (must be zero):</t>
+  </si>
+  <si>
+    <t>The notes referred to above form an integral part of these financial statements.</t>
+  </si>
+  <si>
+    <t>For and on behalf of the Board of Directors</t>
+  </si>
+  <si>
+    <t>NOTES TO FINANCIAL STATEMENTS</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Director</t>
-  </si>
-  <si>
-    <t>Accounts Head</t>
-  </si>
-  <si>
-    <t>Auditor Name</t>
-  </si>
-  <si>
-    <t>Bikash Kumar Acharya</t>
-  </si>
-  <si>
-    <t>Audit Firm</t>
-  </si>
-  <si>
-    <t>B.K. Acharya &amp; Associates</t>
-  </si>
-  <si>
-    <t>Account Name</t>
-  </si>
-  <si>
-    <t>NFRS Category</t>
-  </si>
-  <si>
-    <t>Note</t>
-  </si>
-  <si>
-    <t>Opening Dr</t>
-  </si>
-  <si>
-    <t>Opening Cr</t>
-  </si>
-  <si>
-    <t>During Dr</t>
-  </si>
-  <si>
-    <t>During Cr</t>
-  </si>
-  <si>
-    <t>Adj Dr</t>
-  </si>
-  <si>
-    <t>Adj Cr</t>
-  </si>
-  <si>
-    <t>Closing Dr</t>
-  </si>
-  <si>
-    <t>Closing Cr</t>
-  </si>
-  <si>
-    <t>Net Balance</t>
-  </si>
-  <si>
-    <t>Cash in Hand</t>
-  </si>
-  <si>
-    <t>cash_in_hand</t>
-  </si>
-  <si>
-    <t>NIC Asia Bank Current Account</t>
-  </si>
-  <si>
-    <t>bank_current_account</t>
-  </si>
-  <si>
-    <t>Bank Balance</t>
-  </si>
-  <si>
-    <t>Himalayan Bank FD</t>
-  </si>
-  <si>
-    <t>bank_fixed_deposit_current</t>
-  </si>
-  <si>
-    <t>Fixed Deposit (Current)</t>
-  </si>
-  <si>
-    <t>Debtor - ABC Traders</t>
-  </si>
-  <si>
-    <t>trade_receivables</t>
-  </si>
-  <si>
-    <t>Sundry Debtors</t>
-  </si>
-  <si>
-    <t>Debtor - XYZ Enterprises</t>
-  </si>
-  <si>
-    <t>Advance to Suppliers</t>
-  </si>
-  <si>
-    <t>other_receivables_advance_supplier</t>
-  </si>
-  <si>
-    <t>Closing Stock</t>
-  </si>
-  <si>
-    <t>inventory_finished_goods</t>
-  </si>
-  <si>
-    <t>Finished Goods</t>
-  </si>
-  <si>
-    <t>Building</t>
-  </si>
-  <si>
-    <t>ppe_buildings</t>
-  </si>
-  <si>
-    <t>Buildings</t>
-  </si>
-  <si>
-    <t>Vehicle</t>
-  </si>
-  <si>
-    <t>ppe_vehicles</t>
-  </si>
-  <si>
-    <t>Vehicles</t>
-  </si>
-  <si>
-    <t>Accumulated Depreciation</t>
-  </si>
-  <si>
-    <t>accum_depreciation</t>
-  </si>
-  <si>
-    <t>TDS Receivable</t>
-  </si>
-  <si>
-    <t>other_receivables_tds</t>
-  </si>
-  <si>
-    <t>Creditor - Supplier A</t>
-  </si>
-  <si>
-    <t>trade_payables_creditors</t>
-  </si>
-  <si>
-    <t>Sundry Creditors</t>
-  </si>
-  <si>
-    <t>Creditor - Supplier B</t>
-  </si>
-  <si>
-    <t>Audit Fee Payable</t>
-  </si>
-  <si>
-    <t>audit_fee_payable</t>
-  </si>
-  <si>
-    <t>TDS Payable</t>
-  </si>
-  <si>
-    <t>tds_payable</t>
-  </si>
-  <si>
-    <t>Term Loan - Nabil Bank</t>
-  </si>
-  <si>
-    <t>borrowings_noncurrent_bank</t>
-  </si>
-  <si>
-    <t>Term Loan - Bank</t>
-  </si>
-  <si>
-    <t>Paid-up Capital</t>
-  </si>
-  <si>
-    <t>share_capital</t>
-  </si>
-  <si>
-    <t>General Reserve</t>
-  </si>
-  <si>
-    <t>general_reserve</t>
+    <t>1. STATEMENT OF COMPLIANCE</t>
+  </si>
+  <si>
+    <t>These financial statements of ${params.companyName} have been prepared in accordance with Nepal Accounting Standards for Micro Entities (NAS for MEs) issued by the Institute of Chartered Accountants of Nepal (ICAN).</t>
+  </si>
+  <si>
+    <t>2. BASIS OF PREPARATION</t>
+  </si>
+  <si>
+    <t>These financial statements are prepared on the historical cost basis except for certain financial instruments measured at fair values as described in the accounting policies. The financial statements are presented in Nepalese Rupees (NPR) rounded to the nearest NPR ${params.roundingLevel.toLocaleString('en-IN')}.</t>
+  </si>
+  <si>
+    <t>3. AUTHORIZATION FOR ISSUE</t>
+  </si>
+  <si>
+    <t>These financial statements for the fiscal year ${params.fiscalYear} were authorized for issue by the Board of Directors of ${params.companyName} on ${params.authorizationDate ?? '[Board Meeting Date]'}.</t>
+  </si>
+  <si>
+    <t>Refer to Note 1 (Significant Accounting Policies) and Note 2 (Critical Accounting Judgments) sheets in this workbook for the complete notes to the financial statements.</t>
+  </si>
+  <si>
+    <t>STATEMENT OF INCOME</t>
+  </si>
+  <si>
+    <t>For the Year Ended 31 Ashadh 82</t>
+  </si>
+  <si>
+    <t>2081-80/2081</t>
+  </si>
+  <si>
+    <t>INCOME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Revenue from Operations</t>
+  </si>
+  <si>
+    <t>3.17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Interest Income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Other Income</t>
+  </si>
+  <si>
+    <t>Total Income</t>
+  </si>
+  <si>
+    <t>EXPENSES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Material Consumed</t>
+  </si>
+  <si>
+    <t>3.18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Direct Expenses</t>
+  </si>
+  <si>
+    <t>3.19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Employee Benefit Expenses</t>
+  </si>
+  <si>
+    <t>3.20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Finance Costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Depreciation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Impairment Losses</t>
+  </si>
+  <si>
+    <t>3.21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Administrative &amp; Other Exp</t>
+  </si>
+  <si>
+    <t>3.22</t>
+  </si>
+  <si>
+    <t>Total Expenses</t>
+  </si>
+  <si>
+    <t>Profit/(Loss) before Staff Bonus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Less: Staff Bonus</t>
+  </si>
+  <si>
+    <t>Profit/(Loss) before Tax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Less: Income Tax Expense</t>
+  </si>
+  <si>
+    <t>3.23</t>
+  </si>
+  <si>
+    <t>Net Profit/(Loss) for the Year</t>
+  </si>
+  <si>
+    <t>STATEMENT OF CHANGES IN EQUITY</t>
+  </si>
+  <si>
+    <t>Share Capital</t>
+  </si>
+  <si>
+    <t>Share Premium</t>
   </si>
   <si>
     <t>Retained Earnings</t>
   </si>
   <si>
-    <t>retained_earnings</t>
-  </si>
-  <si>
-    <t>Sales Revenue</t>
-  </si>
-  <si>
-    <t>revenue_sales</t>
-  </si>
-  <si>
-    <t>Changes in Inventory</t>
-  </si>
-  <si>
-    <t>Purchase</t>
-  </si>
-  <si>
-    <t>cogs_purchases</t>
-  </si>
-  <si>
-    <t>Purchases</t>
-  </si>
-  <si>
-    <t>Salary</t>
-  </si>
-  <si>
-    <t>emp_expense_salaries</t>
-  </si>
-  <si>
-    <t>Salaries</t>
-  </si>
-  <si>
-    <t>Provident Fund</t>
-  </si>
-  <si>
-    <t>emp_expense_pf</t>
-  </si>
-  <si>
-    <t>Provident Fund Expense</t>
-  </si>
-  <si>
-    <t>Rent</t>
-  </si>
-  <si>
-    <t>admin_rent</t>
-  </si>
-  <si>
-    <t>Electricity</t>
-  </si>
-  <si>
-    <t>admin_electricity</t>
-  </si>
-  <si>
-    <t>Electricity &amp; Water</t>
-  </si>
-  <si>
-    <t>Interest on Loan</t>
-  </si>
-  <si>
-    <t>finance_cost_interest</t>
-  </si>
-  <si>
-    <t>Interest Expense</t>
-  </si>
-  <si>
-    <t>Audit Fee</t>
-  </si>
-  <si>
-    <t>admin_audit_fee</t>
-  </si>
-  <si>
-    <t>Other Admin Expenses</t>
-  </si>
-  <si>
-    <t>admin_other</t>
-  </si>
-  <si>
-    <t>Other Administrative Expenses</t>
-  </si>
-  <si>
-    <t>VAT Payable</t>
-  </si>
-  <si>
-    <t>other_payables</t>
-  </si>
-  <si>
-    <t>HIMALAYAN TRADING PVT. LTD.</t>
-  </si>
-  <si>
-    <t>STATEMENT OF FINANCIAL POSITION</t>
-  </si>
-  <si>
-    <t>As at 31 Ashadh 82 (15 July 2025)</t>
-  </si>
-  <si>
-    <t>All amounts in NPR (Nepalese Rupees)</t>
-  </si>
-  <si>
-    <t>Particulars</t>
-  </si>
-  <si>
-    <t>31 Ashadh 82</t>
-  </si>
-  <si>
-    <t>A.  NON-CURRENT ASSETS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Property, Plant and Equipment</t>
-  </si>
-  <si>
-    <t>3.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Investments</t>
-  </si>
-  <si>
-    <t>3.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Other Receivables (Non-current)</t>
-  </si>
-  <si>
-    <t>3.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Other Non-Current Assets</t>
-  </si>
-  <si>
-    <t>3.5</t>
-  </si>
-  <si>
-    <t>Total Non-Current Assets</t>
-  </si>
-  <si>
-    <t>B.  CURRENT ASSETS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Investments (Current)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Inventories</t>
-  </si>
-  <si>
-    <t>3.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Trade and Other Receivables</t>
-  </si>
-  <si>
-    <t>3.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Cash and Cash Equivalents</t>
-  </si>
-  <si>
-    <t>3.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Other Current Assets</t>
-  </si>
-  <si>
-    <t>3.6</t>
-  </si>
-  <si>
-    <t>Total Current Assets</t>
-  </si>
-  <si>
-    <t>TOTAL ASSETS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Share Capital</t>
-  </si>
-  <si>
-    <t>3.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Reserves</t>
-  </si>
-  <si>
-    <t>3.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Retained Earnings</t>
-  </si>
-  <si>
-    <t>Total Equity</t>
-  </si>
-  <si>
-    <t>D.  NON-CURRENT LIABILITIES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Loans and Borrowings</t>
-  </si>
-  <si>
-    <t>3.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Employee Benefit Liabilities</t>
-  </si>
-  <si>
-    <t>3.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Provisions</t>
-  </si>
-  <si>
-    <t>Total Non-Current Liabilities</t>
-  </si>
-  <si>
-    <t>E.  CURRENT LIABILITIES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Trade and Other Payables</t>
-  </si>
-  <si>
-    <t>3.13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Income Tax Liability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Employee Benefit Liability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Other Current Liabilities</t>
-  </si>
-  <si>
-    <t>Total Current Liabilities</t>
-  </si>
-  <si>
-    <t>TOTAL EQUITY AND LIABILITIES</t>
-  </si>
-  <si>
-    <t>Balance Check (must be zero):</t>
-  </si>
-  <si>
-    <t>The notes referred to above form an integral part of these financial statements.</t>
-  </si>
-  <si>
-    <t>For and on behalf of the Board of Directors</t>
-  </si>
-  <si>
-    <t>NOTES TO FINANCIAL STATEMENTS</t>
-  </si>
-  <si>
-    <t>1. STATEMENT OF COMPLIANCE</t>
-  </si>
-  <si>
-    <t>These financial statements of ${params.companyName} have been prepared in accordance with Nepal Accounting Standards for Micro Entities (NAS for MEs) issued by the Institute of Chartered Accountants of Nepal (ICAN).</t>
-  </si>
-  <si>
-    <t>2. BASIS OF PREPARATION</t>
-  </si>
-  <si>
-    <t>These financial statements are prepared on the historical cost basis except for certain financial instruments measured at fair values as described in the accounting policies. The financial statements are presented in Nepalese Rupees (NPR) rounded to the nearest NPR ${params.roundingLevel.toLocaleString('en-IN')}.</t>
-  </si>
-  <si>
-    <t>3. AUTHORIZATION FOR ISSUE</t>
-  </si>
-  <si>
-    <t>These financial statements for the fiscal year ${params.fiscalYear} were authorized for issue by the Board of Directors of ${params.companyName} on ${params.authorizationDate ?? '[Board Meeting Date]'}.</t>
-  </si>
-  <si>
-    <t>Refer to Note 1 (Significant Accounting Policies) and Note 2 (Critical Accounting Judgments) sheets in this workbook for the complete notes to the financial statements.</t>
-  </si>
-  <si>
-    <t>STATEMENT OF INCOME</t>
-  </si>
-  <si>
-    <t>For the Year Ended 31 Ashadh 82</t>
-  </si>
-  <si>
-    <t>2081-80/2081</t>
-  </si>
-  <si>
-    <t>INCOME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Revenue from Operations</t>
-  </si>
-  <si>
-    <t>3.17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Interest Income</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Other Income</t>
-  </si>
-  <si>
-    <t>Total Income</t>
-  </si>
-  <si>
-    <t>EXPENSES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Material Consumed</t>
-  </si>
-  <si>
-    <t>3.18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Direct Expenses</t>
-  </si>
-  <si>
-    <t>3.19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Employee Benefit Expenses</t>
-  </si>
-  <si>
-    <t>3.20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Finance Costs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Depreciation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Impairment Losses</t>
-  </si>
-  <si>
-    <t>3.21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Administrative &amp; Other Exp</t>
-  </si>
-  <si>
-    <t>3.22</t>
-  </si>
-  <si>
-    <t>Total Expenses</t>
-  </si>
-  <si>
-    <t>Profit/(Loss) before Staff Bonus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Less: Staff Bonus</t>
-  </si>
-  <si>
-    <t>Profit/(Loss) before Tax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Less: Income Tax Expense</t>
-  </si>
-  <si>
-    <t>3.23</t>
-  </si>
-  <si>
-    <t>Net Profit/(Loss) for the Year</t>
-  </si>
-  <si>
-    <t>STATEMENT OF CHANGES IN EQUITY</t>
-  </si>
-  <si>
-    <t>Share Capital</t>
-  </si>
-  <si>
-    <t>Share Premium</t>
-  </si>
-  <si>
     <t>Total</t>
   </si>
   <si>
@@ -1203,10 +1557,10 @@
     <t xml:space="preserve">  Reconciliation Difference (should be zero)</t>
   </si>
   <si>
-    <t>For B.K. Acharya &amp; Associates</t>
-  </si>
-  <si>
-    <t>Partner</t>
+    <t>For A &amp; Associates</t>
+  </si>
+  <si>
+    <t>Proprietor</t>
   </si>
   <si>
     <t>Notes to the Financial Statements for the Year Ended 2081/82</t>
@@ -1224,7 +1578,7 @@
     <t>1.2 Basis of Preparation</t>
   </si>
   <si>
-    <t>These financial statements are prepared on the historical cost basis, except for certain financial instruments and investment properties that are measured at fair value as described in the relevant policies below. The financial statements are presented in Nepalese Rupees (NPR) and rounded to the nearest NPR 1.</t>
+    <t>These financial statements are prepared on the historical cost basis, except for certain financial instruments and investment properties that are measured at fair value as described in the relevant policies below. The financial statements are presented in Nepalese Rupees (NPR) and rounded to the nearest NPR 100.</t>
   </si>
   <si>
     <t>The financial statements are prepared on the going concern basis. The management has assessed the company's ability to continue as a going concern for the foreseeable future and is not aware of any material uncertainties that may cast significant doubt on this assessment.</t>
@@ -1320,7 +1674,7 @@
     <t>1.12 Authorization for Issue</t>
   </si>
   <si>
-    <t>These financial statements were authorized for issue by the Board of Directors of Himalayan Trading Pvt. Ltd. on [Date].</t>
+    <t>These financial statements were authorized for issue by the Board of Directors of ABC PRIVATE LIMITED on [Date].</t>
   </si>
   <si>
     <t>NOTE 2: CRITICAL ACCOUNTING JUDGMENTS AND KEY SOURCES OF ESTIMATION UNCERTAINTY</t>
@@ -1383,6 +1737,9 @@
     <t>3.1  Property, Plant and Equipment</t>
   </si>
   <si>
+    <t>Intangibles / Software</t>
+  </si>
+  <si>
     <t>COST</t>
   </si>
   <si>
@@ -1434,48 +1791,30 @@
     <t>3.4  Other Receivables</t>
   </si>
   <si>
-    <t>VAT Receivable</t>
-  </si>
-  <si>
-    <t>Prepayments</t>
-  </si>
-  <si>
-    <t>Accrued Income</t>
-  </si>
-  <si>
-    <t>Staff Advances</t>
-  </si>
-  <si>
-    <t>Loans &amp; Advances to Others</t>
-  </si>
-  <si>
-    <t>Other Current Assets</t>
+    <t>Security Deposits</t>
+  </si>
+  <si>
+    <t>Advance Income Tax</t>
+  </si>
+  <si>
+    <t>Other Prepaid Expenses</t>
   </si>
   <si>
     <t>3.5  Other Non-Current Assets</t>
   </si>
   <si>
-    <t>Long-term Loans &amp; Advances</t>
-  </si>
-  <si>
-    <t>Security Deposits</t>
-  </si>
-  <si>
-    <t>Deferred Tax Asset</t>
-  </si>
-  <si>
     <t>3.6  Other Current Assets</t>
   </si>
   <si>
+    <t>Held for Sale</t>
+  </si>
+  <si>
     <t>3.7  Inventories</t>
   </si>
   <si>
     <t>Raw Materials and Consumables</t>
   </si>
   <si>
-    <t>Work in Progress</t>
-  </si>
-  <si>
     <t>Finished Goods and Goods for Resale</t>
   </si>
   <si>
@@ -1500,9 +1839,6 @@
     <t>3.10  Reserves</t>
   </si>
   <si>
-    <t>Other Reserves</t>
-  </si>
-  <si>
     <t>3.11  Loans and Borrowings</t>
   </si>
   <si>
@@ -1518,45 +1854,27 @@
     <t>Security</t>
   </si>
   <si>
-    <t>0%</t>
-  </si>
-  <si>
     <t>Current Borrowings</t>
   </si>
   <si>
     <t>3.12  Employee Benefits</t>
   </si>
   <si>
-    <t>salaryPayable</t>
-  </si>
-  <si>
-    <t>bonusPayable</t>
-  </si>
-  <si>
-    <t>pfPayable</t>
-  </si>
-  <si>
-    <t>gratuity</t>
-  </si>
-  <si>
-    <t>leaveEncashment</t>
+    <t>Gratuity</t>
+  </si>
+  <si>
+    <t>Bonus Payable</t>
   </si>
   <si>
     <t>3.13  Trade and Other Payables</t>
   </si>
   <si>
-    <t>Trade Creditors (Sundry Creditors)</t>
+    <t>Trade Creditors</t>
   </si>
   <si>
     <t>Advance from Customers</t>
   </si>
   <si>
-    <t>TDS / Withholding Tax Payable</t>
-  </si>
-  <si>
-    <t>Other Payables</t>
-  </si>
-  <si>
     <t>3.14  Provisions</t>
   </si>
   <si>
@@ -1569,18 +1887,6 @@
     <t>Rendering of Services</t>
   </si>
   <si>
-    <t>Interest Income</t>
-  </si>
-  <si>
-    <t>Dividend Income</t>
-  </si>
-  <si>
-    <t>Rental Income</t>
-  </si>
-  <si>
-    <t>Other Income</t>
-  </si>
-  <si>
     <t>3.18  Material Consumed</t>
   </si>
   <si>
@@ -1596,34 +1902,10 @@
     <t>3.19  Direct Expenses</t>
   </si>
   <si>
-    <t>Direct Wages &amp; Labour</t>
-  </si>
-  <si>
-    <t>Other Direct Expenses</t>
-  </si>
-  <si>
     <t>3.20  Employee Benefit Expenses</t>
   </si>
   <si>
-    <t>Salaries, Wages &amp; Allowances</t>
-  </si>
-  <si>
-    <t>PF / SSF Contribution (Employer's)</t>
-  </si>
-  <si>
-    <t>Gratuity Expense</t>
-  </si>
-  <si>
-    <t>Leave Encashment Expense</t>
-  </si>
-  <si>
-    <t>Staff Bonus (10% of Net Profit before Tax)</t>
-  </si>
-  <si>
-    <t>Staff Welfare &amp; Training</t>
-  </si>
-  <si>
-    <t>Other Employee Benefits</t>
+    <t>Other Employee Costs</t>
   </si>
   <si>
     <t>3.21  Impairment</t>
@@ -1632,19 +1914,16 @@
     <t>3.22  Administrative Expenses</t>
   </si>
   <si>
-    <t>Rent Expense</t>
-  </si>
-  <si>
-    <t>Electricity, Water &amp; Utilities</t>
-  </si>
-  <si>
-    <t>Audit Fee (Statutory &amp; Tax)</t>
-  </si>
-  <si>
-    <t>Selling &amp; Distribution Expenses</t>
-  </si>
-  <si>
-    <t>Miscellaneous Expenses</t>
+    <t>Rent / Lease Rentals</t>
+  </si>
+  <si>
+    <t>Travel &amp; Conveyance</t>
+  </si>
+  <si>
+    <t>Audit Fees</t>
+  </si>
+  <si>
+    <t>CSR &amp; Other Miscellaneous</t>
   </si>
   <si>
     <t>3.23  Income Tax</t>
@@ -1653,19 +1932,19 @@
     <t>Profit Before Tax (per Income Statement)</t>
   </si>
   <si>
-    <t>Add: Provisions (Gratuity/Leave)</t>
-  </si>
-  <si>
     <t>Add: Accounting Depreciation</t>
   </si>
   <si>
-    <t>Less: Tax Depreciation (s.19)</t>
+    <t>Add: Provisions (non-deductible)</t>
+  </si>
+  <si>
+    <t>Less: Tax Depreciation (ITA 2058)</t>
   </si>
   <si>
     <t>Taxable Income</t>
   </si>
   <si>
-    <t>Income Tax at 25%</t>
+    <t>Income Tax at 23%</t>
   </si>
   <si>
     <t>Less: Advance Tax / TDS Credit</t>
@@ -1701,7 +1980,7 @@
     <t>Income Tax Computation</t>
   </si>
   <si>
-    <t>Tax Rate: 25%</t>
+    <t>Tax Rate: 23%</t>
   </si>
   <si>
     <t>Profit Before Tax</t>
@@ -1720,9 +1999,6 @@
   </si>
   <si>
     <t>Current</t>
-  </si>
-  <si>
-    <t>FD (≤3 months)</t>
   </si>
 </sst>
 </file>
@@ -2878,44 +3154,44 @@
         <v>103</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>104</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>108</v>
+        <v>52</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>110</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B36" s="8">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B37" s="8">
         <v>25</v>
@@ -2923,7 +3199,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B38" s="8">
         <v>10</v>
@@ -2931,23 +3207,23 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -2957,24 +3233,24 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="9" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C56" s="12">
         <f>'Balance Sheet'!C50-'Balance Sheet'!C80</f>
@@ -2987,10 +3263,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C57" s="12">
         <f>'Cash Flow'!C60-'Balance Sheet'!C35</f>
@@ -3003,10 +3279,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C58" s="12">
         <f>'Trial Balance'!C5-'Trial Balance'!D5</f>
@@ -3019,10 +3295,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C59" s="12">
         <f>'Income Statement'!C45-'Changes in Equity'!F15</f>
@@ -3059,114 +3335,114 @@
     </row>
     <row r="2" ht="15" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B2" s="51" t="s">
-        <v>383</v>
+        <v>501</v>
       </c>
     </row>
     <row r="3" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" s="50" t="s">
-        <v>421</v>
+        <v>539</v>
       </c>
     </row>
     <row r="5" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" ht="56" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B6" s="51" t="s">
-        <v>422</v>
+        <v>540</v>
       </c>
     </row>
     <row r="7" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="42" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B8" s="51" t="s">
-        <v>423</v>
+        <v>541</v>
       </c>
     </row>
     <row r="9" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="10" ht="18" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B10" s="52" t="s">
-        <v>424</v>
+        <v>542</v>
       </c>
     </row>
     <row r="11" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" ht="18" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B12" s="52" t="s">
-        <v>425</v>
+        <v>543</v>
       </c>
     </row>
     <row r="13" ht="56" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B13" s="51" t="s">
-        <v>426</v>
+        <v>544</v>
       </c>
     </row>
     <row r="14" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="15" ht="18" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B15" s="52" t="s">
-        <v>427</v>
+        <v>545</v>
       </c>
     </row>
     <row r="16" ht="56" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B16" s="51" t="s">
-        <v>428</v>
+        <v>546</v>
       </c>
     </row>
     <row r="17" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="18" ht="18" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="52" t="s">
-        <v>429</v>
+        <v>547</v>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" s="51" t="s">
-        <v>430</v>
+        <v>548</v>
       </c>
     </row>
     <row r="20" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="21" ht="18" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" s="52" t="s">
-        <v>431</v>
+        <v>549</v>
       </c>
     </row>
     <row r="22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" ht="18" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" s="52" t="s">
-        <v>432</v>
+        <v>550</v>
       </c>
     </row>
     <row r="24" ht="56" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" s="51" t="s">
-        <v>433</v>
+        <v>551</v>
       </c>
     </row>
     <row r="25" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" ht="18" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" s="52" t="s">
-        <v>434</v>
+        <v>552</v>
       </c>
     </row>
     <row r="27" ht="42" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" s="51" t="s">
-        <v>435</v>
+        <v>553</v>
       </c>
     </row>
     <row r="28" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="29" ht="18" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" s="52" t="s">
-        <v>436</v>
+        <v>554</v>
       </c>
     </row>
     <row r="30" ht="42" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" s="51" t="s">
-        <v>437</v>
+        <v>555</v>
       </c>
     </row>
     <row r="31" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="32" ht="18" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B32" s="52" t="s">
-        <v>438</v>
+        <v>556</v>
       </c>
     </row>
     <row r="33" ht="70" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B33" s="51" t="s">
-        <v>439</v>
+        <v>557</v>
       </c>
     </row>
     <row r="34" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3180,7 +3456,7 @@
   <sheetPr>
     <tabColor rgb="FF16A34A"/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -3190,158 +3466,224 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="53" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="45" t="s">
-        <v>245</v>
+        <v>361</v>
       </c>
       <c r="B3" s="46" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="C3" s="46" t="s">
-        <v>192</v>
+        <v>215</v>
       </c>
       <c r="D3" s="46" t="s">
-        <v>333</v>
+        <v>216</v>
+      </c>
+      <c r="E3" s="46" t="s">
+        <v>221</v>
+      </c>
+      <c r="F3" s="46" t="s">
+        <v>222</v>
+      </c>
+      <c r="G3" s="46" t="s">
+        <v>559</v>
+      </c>
+      <c r="H3" s="46" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="54" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>442</v>
+        <v>561</v>
       </c>
       <c r="B5" s="55">
-        <v>2500000</v>
+        <v>37190767</v>
       </c>
       <c r="C5" s="55">
-        <v>1200000</v>
+        <v>11500000</v>
       </c>
       <c r="D5" s="55">
-        <v>3700000</v>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1900000</v>
+      </c>
+      <c r="E5" s="55">
+        <v>1700000</v>
+      </c>
+      <c r="F5" s="55">
+        <v>2200000</v>
+      </c>
+      <c r="G5" s="55">
+        <v>165000</v>
+      </c>
+      <c r="H5" s="55">
+        <v>54655767</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>443</v>
+        <v>562</v>
       </c>
       <c r="B6" s="55"/>
       <c r="C6" s="55"/>
       <c r="D6" s="55"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6" s="55"/>
+      <c r="F6" s="55"/>
+      <c r="G6" s="55"/>
+      <c r="H6" s="55"/>
+    </row>
+    <row r="7" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>444</v>
+        <v>563</v>
       </c>
       <c r="B7" s="55"/>
       <c r="C7" s="55"/>
       <c r="D7" s="55"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7" s="55"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="55"/>
+      <c r="H7" s="55"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>445</v>
+        <v>564</v>
       </c>
       <c r="B8" s="55">
-        <v>2500000</v>
+        <v>37190767</v>
       </c>
       <c r="C8" s="55">
-        <v>1200000</v>
+        <v>11500000</v>
       </c>
       <c r="D8" s="55">
-        <v>3700000</v>
+        <v>1900000</v>
+      </c>
+      <c r="E8" s="55">
+        <v>1700000</v>
+      </c>
+      <c r="F8" s="55">
+        <v>2200000</v>
+      </c>
+      <c r="G8" s="55">
+        <v>165000</v>
+      </c>
+      <c r="H8" s="55">
+        <v>54655767</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="54" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>442</v>
-      </c>
-      <c r="B10" s="55">
-        <v>450000</v>
-      </c>
-      <c r="C10" s="55">
-        <v>200000</v>
-      </c>
-      <c r="D10" s="55">
-        <v>650000</v>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>561</v>
+      </c>
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
+      <c r="F10" s="55"/>
+      <c r="G10" s="55"/>
+      <c r="H10" s="55"/>
+    </row>
+    <row r="11" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>447</v>
-      </c>
-      <c r="B11" s="55">
-        <v>100000</v>
-      </c>
-      <c r="C11" s="55">
-        <v>50000</v>
-      </c>
-      <c r="D11" s="55">
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>566</v>
+      </c>
+      <c r="B11" s="55"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="55"/>
+      <c r="E11" s="55"/>
+      <c r="F11" s="55"/>
+      <c r="G11" s="55"/>
+      <c r="H11" s="55"/>
+    </row>
+    <row r="12" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>448</v>
+        <v>567</v>
       </c>
       <c r="B12" s="55"/>
       <c r="C12" s="55"/>
       <c r="D12" s="55"/>
-    </row>
-    <row r="13" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E12" s="55"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="55"/>
+    </row>
+    <row r="13" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>445</v>
-      </c>
-      <c r="B13" s="55">
-        <v>550000</v>
-      </c>
-      <c r="C13" s="55">
-        <v>250000</v>
-      </c>
-      <c r="D13" s="55">
-        <v>800000</v>
-      </c>
+        <v>564</v>
+      </c>
+      <c r="B13" s="55"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="55"/>
+      <c r="E13" s="55"/>
+      <c r="F13" s="55"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="55"/>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="54" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
-        <v>450</v>
+        <v>569</v>
       </c>
       <c r="B15" s="56">
-        <v>2050000</v>
+        <v>37190767</v>
       </c>
       <c r="C15" s="56">
-        <v>1000000</v>
+        <v>11500000</v>
       </c>
       <c r="D15" s="56">
-        <v>3050000</v>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1900000</v>
+      </c>
+      <c r="E15" s="56">
+        <v>1700000</v>
+      </c>
+      <c r="F15" s="56">
+        <v>2200000</v>
+      </c>
+      <c r="G15" s="56">
+        <v>165000</v>
+      </c>
+      <c r="H15" s="56">
+        <v>54655767</v>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
-        <v>451</v>
+        <v>570</v>
       </c>
       <c r="B16" s="56">
-        <v>1950000</v>
+        <v>37190767</v>
       </c>
       <c r="C16" s="56">
-        <v>950000</v>
+        <v>11500000</v>
       </c>
       <c r="D16" s="56">
-        <v>2900000</v>
+        <v>1900000</v>
+      </c>
+      <c r="E16" s="56">
+        <v>1700000</v>
+      </c>
+      <c r="F16" s="56">
+        <v>2200000</v>
+      </c>
+      <c r="G16" s="56">
+        <v>165000</v>
+      </c>
+      <c r="H16" s="56">
+        <v>54655767</v>
       </c>
     </row>
   </sheetData>
@@ -3365,18 +3707,18 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="53" t="s">
-        <v>452</v>
+        <v>571</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>245</v>
+        <v>361</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>453</v>
+        <v>572</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>454</v>
+        <v>573</v>
       </c>
     </row>
   </sheetData>
@@ -3400,26 +3742,30 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="53" t="s">
-        <v>455</v>
+        <v>574</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>245</v>
+        <v>361</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>453</v>
+        <v>572</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>454</v>
+        <v>573</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>456</v>
-      </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
+        <v>575</v>
+      </c>
+      <c r="B4" s="55">
+        <v>1327000</v>
+      </c>
+      <c r="C4" s="55">
+        <v>1377000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3428,90 +3774,6 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor rgb="FF16A34A"/>
-  </sheetPr>
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="42" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="4" width="18" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="53" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>453</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>195</v>
-      </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>458</v>
-      </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="55"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>459</v>
-      </c>
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>460</v>
-      </c>
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>461</v>
-      </c>
-      <c r="B8" s="55"/>
-      <c r="C8" s="55"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>462</v>
-      </c>
-      <c r="B9" s="55"/>
-      <c r="C9" s="55"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>463</v>
-      </c>
-      <c r="B10" s="55"/>
-      <c r="C10" s="55"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF16A34A"/>
@@ -3526,40 +3788,86 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="53" t="s">
-        <v>464</v>
+        <v>576</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>245</v>
+        <v>361</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>453</v>
+        <v>572</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>454</v>
+        <v>573</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>465</v>
+        <v>577</v>
+      </c>
+      <c r="B4" s="55">
+        <v>275000</v>
+      </c>
+      <c r="C4" s="55"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>578</v>
+      </c>
+      <c r="B5" s="55"/>
+      <c r="C5" s="55"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>579</v>
+      </c>
+      <c r="B6" s="55">
+        <v>10000</v>
+      </c>
+      <c r="C6" s="55"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF16A34A"/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="42" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="4" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="53" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
+        <v>361</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>572</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>231</v>
       </c>
       <c r="B4" s="55"/>
       <c r="C4" s="55"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>466</v>
-      </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="55"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>467</v>
-      </c>
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3572,7 +3880,7 @@
   <sheetPr>
     <tabColor rgb="FF16A34A"/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -3582,19 +3890,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="53" t="s">
-        <v>468</v>
+        <v>581</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>245</v>
+        <v>361</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>453</v>
+        <v>572</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>454</v>
-      </c>
+        <v>573</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>582</v>
+      </c>
+      <c r="B4" s="55"/>
+      <c r="C4" s="55"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3617,47 +3932,59 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="53" t="s">
-        <v>469</v>
+        <v>583</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>245</v>
+        <v>361</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>453</v>
+        <v>572</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>454</v>
+        <v>573</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>470</v>
+        <v>584</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>471</v>
-      </c>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
+        <v>230</v>
+      </c>
+      <c r="B5" s="20">
+        <v>2800000</v>
+      </c>
+      <c r="C5" s="20">
+        <v>2800000</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>472</v>
-      </c>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
+        <v>585</v>
+      </c>
+      <c r="B6" s="20">
+        <v>25000</v>
+      </c>
+      <c r="C6" s="20">
+        <v>25000</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
-        <v>333</v>
-      </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="48"/>
+        <v>451</v>
+      </c>
+      <c r="B7" s="48">
+        <v>2825000</v>
+      </c>
+      <c r="C7" s="48">
+        <v>2825000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3670,7 +3997,7 @@
   <sheetPr>
     <tabColor rgb="FF16A34A"/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -3680,50 +4007,66 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="53" t="s">
-        <v>473</v>
+        <v>586</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>245</v>
+        <v>361</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>453</v>
+        <v>572</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>454</v>
+        <v>573</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>170</v>
+        <v>263</v>
       </c>
       <c r="B4" s="55">
-        <v>50000</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B5" s="55">
-        <v>250000</v>
+        <v>-1500000</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B6" s="55">
-        <v>500000</v>
+        <v>-1000000</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
-        <v>474</v>
-      </c>
-      <c r="B7" s="56">
-        <v>800000</v>
+      <c r="A7" t="s">
+        <v>264</v>
+      </c>
+      <c r="B7" s="55">
+        <v>115000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>265</v>
+      </c>
+      <c r="B8" s="55">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
+        <v>587</v>
+      </c>
+      <c r="B9" s="56">
+        <v>-2289000</v>
       </c>
     </row>
   </sheetData>
@@ -3747,26 +4090,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="53" t="s">
-        <v>475</v>
+        <v>588</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>476</v>
-      </c>
-      <c r="B3" s="55"/>
+        <v>589</v>
+      </c>
+      <c r="B3" s="55">
+        <v>510000</v>
+      </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>477</v>
-      </c>
-      <c r="B4" s="55"/>
+        <v>590</v>
+      </c>
+      <c r="B4" s="55">
+        <v>510000</v>
+      </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>478</v>
-      </c>
-      <c r="B5" s="55"/>
+        <v>591</v>
+      </c>
+      <c r="B5" s="55">
+        <v>51000000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3789,71 +4138,71 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -3863,6 +4212,141 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF16A34A"/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="42" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="4" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="53" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
+        <v>361</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>572</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>449</v>
+      </c>
+      <c r="B4" s="55"/>
+      <c r="C4" s="55"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B5" s="55">
+        <v>2532000</v>
+      </c>
+      <c r="C5" s="55">
+        <v>2532000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>450</v>
+      </c>
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF16A34A"/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="42" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="4" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="53" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="54" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
+        <v>595</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>596</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>597</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>572</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="54" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>354</v>
+      </c>
+      <c r="B6" t="s">
+        <v>354</v>
+      </c>
+      <c r="D6" s="55">
+        <v>100000</v>
+      </c>
+      <c r="E6" s="55"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>356</v>
+      </c>
+      <c r="B7" t="s">
+        <v>356</v>
+      </c>
+      <c r="D7" s="55">
+        <v>50000</v>
+      </c>
+      <c r="E7" s="55"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF16A34A"/>
@@ -3877,180 +4361,51 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="53" t="s">
-        <v>479</v>
+        <v>599</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>245</v>
+        <v>361</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>453</v>
+        <v>572</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>454</v>
+        <v>573</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>210</v>
+        <v>600</v>
       </c>
       <c r="B4" s="55"/>
       <c r="C4" s="55"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>332</v>
+        <v>309</v>
       </c>
       <c r="B5" s="55"/>
       <c r="C5" s="55"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>212</v>
-      </c>
-      <c r="B6" s="55"/>
+        <v>193</v>
+      </c>
+      <c r="B6" s="55">
+        <v>50000</v>
+      </c>
       <c r="C6" s="55"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>480</v>
-      </c>
-      <c r="B7" s="55"/>
+        <v>601</v>
+      </c>
+      <c r="B7" s="55">
+        <v>247349</v>
+      </c>
       <c r="C7" s="55"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor rgb="FF16A34A"/>
-  </sheetPr>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="42" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="4" width="18" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="53" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="54" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>483</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>484</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>485</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>453</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>205</v>
-      </c>
-      <c r="B4" t="s">
-        <v>486</v>
-      </c>
-      <c r="D4" s="55">
-        <v>800000</v>
-      </c>
-      <c r="E4" s="55"/>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="54" t="s">
-        <v>487</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor rgb="FF16A34A"/>
-  </sheetPr>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="42" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="4" width="18" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="53" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>453</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>489</v>
-      </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>490</v>
-      </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="55"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>491</v>
-      </c>
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>492</v>
-      </c>
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>493</v>
-      </c>
-      <c r="B8" s="55"/>
-      <c r="C8" s="55"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4073,54 +4428,70 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="53" t="s">
-        <v>494</v>
+        <v>602</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>245</v>
+        <v>361</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>453</v>
+        <v>572</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>454</v>
+        <v>573</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>495</v>
-      </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
+        <v>603</v>
+      </c>
+      <c r="B4" s="55">
+        <v>675000</v>
+      </c>
+      <c r="C4" s="55">
+        <v>180000</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>496</v>
+        <v>604</v>
       </c>
       <c r="B5" s="55"/>
       <c r="C5" s="55"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>201</v>
-      </c>
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
+        <v>182</v>
+      </c>
+      <c r="B6" s="55">
+        <v>150000</v>
+      </c>
+      <c r="C6" s="55">
+        <v>115000</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>497</v>
-      </c>
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
+        <v>208</v>
+      </c>
+      <c r="B7" s="55">
+        <v>30000</v>
+      </c>
+      <c r="C7" s="55">
+        <v>15000</v>
+      </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>498</v>
-      </c>
-      <c r="B8" s="55"/>
-      <c r="C8" s="55"/>
+        <v>199</v>
+      </c>
+      <c r="B8" s="55">
+        <v>110000</v>
+      </c>
+      <c r="C8" s="55">
+        <v>80000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4143,18 +4514,18 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="53" t="s">
-        <v>499</v>
+        <v>605</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>245</v>
+        <v>361</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>453</v>
+        <v>572</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>454</v>
+        <v>573</v>
       </c>
     </row>
   </sheetData>
@@ -4168,7 +4539,7 @@
   <sheetPr>
     <tabColor rgb="FF16A34A"/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -4178,61 +4549,55 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="53" t="s">
-        <v>500</v>
+        <v>606</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>245</v>
+        <v>361</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>453</v>
+        <v>572</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>454</v>
+        <v>573</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>501</v>
-      </c>
-      <c r="B4" s="55"/>
+        <v>607</v>
+      </c>
+      <c r="B4" s="55">
+        <v>9000000</v>
+      </c>
       <c r="C4" s="55"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>502</v>
-      </c>
-      <c r="B5" s="55"/>
+        <v>608</v>
+      </c>
+      <c r="B5" s="55">
+        <v>1500000</v>
+      </c>
       <c r="C5" s="55"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>503</v>
-      </c>
-      <c r="B6" s="55"/>
+        <v>288</v>
+      </c>
+      <c r="B6" s="55">
+        <v>2000</v>
+      </c>
       <c r="C6" s="55"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>504</v>
-      </c>
-      <c r="B7" s="55"/>
+        <v>293</v>
+      </c>
+      <c r="B7" s="55">
+        <v>72000</v>
+      </c>
       <c r="C7" s="55"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>505</v>
-      </c>
-      <c r="B8" s="55"/>
-      <c r="C8" s="55"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>506</v>
-      </c>
-      <c r="B9" s="55"/>
-      <c r="C9" s="55"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4255,46 +4620,50 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="53" t="s">
-        <v>507</v>
+        <v>609</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>245</v>
+        <v>361</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>453</v>
+        <v>572</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>454</v>
+        <v>573</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>508</v>
+        <v>610</v>
       </c>
       <c r="B4" s="55"/>
       <c r="C4" s="55"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>219</v>
-      </c>
-      <c r="B5" s="55"/>
+        <v>281</v>
+      </c>
+      <c r="B5" s="55">
+        <v>6000000</v>
+      </c>
       <c r="C5" s="55"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>509</v>
+        <v>611</v>
       </c>
       <c r="B6" s="55"/>
       <c r="C6" s="55"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>510</v>
-      </c>
-      <c r="B7" s="55"/>
+        <v>612</v>
+      </c>
+      <c r="B7" s="55">
+        <v>6000000</v>
+      </c>
       <c r="C7" s="55"/>
     </row>
   </sheetData>
@@ -4318,32 +4687,36 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="53" t="s">
-        <v>511</v>
+        <v>613</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>245</v>
+        <v>361</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>453</v>
+        <v>572</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>454</v>
+        <v>573</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>512</v>
-      </c>
-      <c r="B4" s="55"/>
+        <v>284</v>
+      </c>
+      <c r="B4" s="55">
+        <v>500000</v>
+      </c>
       <c r="C4" s="55"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>513</v>
-      </c>
-      <c r="B5" s="55"/>
+        <v>285</v>
+      </c>
+      <c r="B5" s="55">
+        <v>100000</v>
+      </c>
       <c r="C5" s="55"/>
     </row>
   </sheetData>
@@ -4357,7 +4730,7 @@
   <sheetPr>
     <tabColor rgb="FF16A34A"/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -4367,68 +4740,69 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="53" t="s">
-        <v>514</v>
+        <v>614</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>245</v>
+        <v>361</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>453</v>
+        <v>572</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>454</v>
+        <v>573</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>515</v>
-      </c>
-      <c r="B4" s="55"/>
+        <v>298</v>
+      </c>
+      <c r="B4" s="55">
+        <v>500000</v>
+      </c>
       <c r="C4" s="55"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>516</v>
-      </c>
-      <c r="B5" s="55"/>
+        <v>304</v>
+      </c>
+      <c r="B5" s="55">
+        <v>100000</v>
+      </c>
       <c r="C5" s="55"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>517</v>
+        <v>600</v>
       </c>
       <c r="B6" s="55"/>
       <c r="C6" s="55"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>518</v>
-      </c>
-      <c r="B7" s="55"/>
+        <v>307</v>
+      </c>
+      <c r="B7" s="55">
+        <v>209600</v>
+      </c>
       <c r="C7" s="55"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>519</v>
-      </c>
-      <c r="B8" s="55"/>
+        <v>303</v>
+      </c>
+      <c r="B8" s="55">
+        <v>170000</v>
+      </c>
       <c r="C8" s="55"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>520</v>
+        <v>615</v>
       </c>
       <c r="B9" s="55"/>
       <c r="C9" s="55"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>521</v>
-      </c>
-      <c r="B10" s="55"/>
-      <c r="C10" s="55"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4441,7 +4815,7 @@
   <sheetPr>
     <tabColor rgb="FF16A34A"/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -4451,19 +4825,28 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="53" t="s">
-        <v>522</v>
+        <v>616</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>245</v>
+        <v>361</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>453</v>
+        <v>572</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>454</v>
-      </c>
+        <v>573</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>318</v>
+      </c>
+      <c r="B4" s="55">
+        <v>300000</v>
+      </c>
+      <c r="C4" s="55"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4494,26 +4877,26 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -4526,23 +4909,23 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>151</v>
@@ -4550,18 +4933,18 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -4575,7 +4958,7 @@
   <sheetPr>
     <tabColor rgb="FF16A34A"/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -4585,61 +4968,91 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="53" t="s">
-        <v>523</v>
+        <v>617</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>245</v>
+        <v>361</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>453</v>
+        <v>572</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>454</v>
+        <v>573</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>524</v>
-      </c>
-      <c r="B4" s="55"/>
+        <v>618</v>
+      </c>
+      <c r="B4" s="55">
+        <v>50000</v>
+      </c>
       <c r="C4" s="55"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>525</v>
-      </c>
-      <c r="B5" s="55"/>
+        <v>347</v>
+      </c>
+      <c r="B5" s="55">
+        <v>10000</v>
+      </c>
       <c r="C5" s="55"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>526</v>
-      </c>
-      <c r="B6" s="55"/>
+        <v>619</v>
+      </c>
+      <c r="B6" s="55">
+        <v>70000</v>
+      </c>
       <c r="C6" s="55"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>527</v>
-      </c>
-      <c r="B7" s="55"/>
+        <v>620</v>
+      </c>
+      <c r="B7" s="55">
+        <v>25000</v>
+      </c>
       <c r="C7" s="55"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>528</v>
-      </c>
-      <c r="B8" s="55"/>
+        <v>324</v>
+      </c>
+      <c r="B8" s="55">
+        <v>51000</v>
+      </c>
       <c r="C8" s="55"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>238</v>
-      </c>
-      <c r="B9" s="55"/>
+        <v>342</v>
+      </c>
+      <c r="B9" s="55">
+        <v>20000</v>
+      </c>
       <c r="C9" s="55"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>314</v>
+      </c>
+      <c r="B10" s="55">
+        <v>10000</v>
+      </c>
+      <c r="C10" s="55"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>621</v>
+      </c>
+      <c r="B11" s="55">
+        <v>145000</v>
+      </c>
+      <c r="C11" s="55"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4662,62 +5075,64 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="53" t="s">
-        <v>529</v>
+        <v>622</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>530</v>
+        <v>623</v>
       </c>
       <c r="B3" s="55">
-        <v>549450</v>
+        <v>1886400</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>531</v>
-      </c>
-      <c r="B4" s="55"/>
+        <v>624</v>
+      </c>
+      <c r="B4" s="55">
+        <v>150000</v>
+      </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>532</v>
-      </c>
-      <c r="B5" s="55">
-        <v>150000</v>
-      </c>
+        <v>625</v>
+      </c>
+      <c r="B5" s="55"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>533</v>
-      </c>
-      <c r="B6" s="55"/>
+        <v>626</v>
+      </c>
+      <c r="B6" s="55">
+        <v>-305000</v>
+      </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>534</v>
+        <v>627</v>
       </c>
       <c r="B7" s="55">
-        <v>699450</v>
+        <v>1731400</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>535</v>
+        <v>628</v>
       </c>
       <c r="B8" s="55">
-        <v>1748.63</v>
+        <v>4328.5</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>536</v>
+        <v>629</v>
       </c>
       <c r="B9" s="55"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>537</v>
+        <v>630</v>
       </c>
       <c r="B10" s="55"/>
     </row>
@@ -4742,30 +5157,30 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="53" t="s">
-        <v>538</v>
+        <v>631</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>539</v>
+        <v>632</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>540</v>
+        <v>633</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>541</v>
+        <v>634</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>542</v>
+        <v>635</v>
       </c>
       <c r="E3" s="18" t="s">
-        <v>543</v>
+        <v>636</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>544</v>
+        <v>637</v>
       </c>
       <c r="G3" s="18" t="s">
-        <v>545</v>
+        <v>638</v>
       </c>
     </row>
   </sheetData>
@@ -4789,67 +5204,71 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="53" t="s">
-        <v>546</v>
+        <v>639</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>547</v>
+        <v>640</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>548</v>
+        <v>641</v>
       </c>
       <c r="B4" s="55">
-        <v>549450</v>
+        <v>1886400</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>531</v>
-      </c>
-      <c r="B5" s="55"/>
+        <v>624</v>
+      </c>
+      <c r="B5" s="55">
+        <v>150000</v>
+      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>532</v>
-      </c>
-      <c r="B6" s="55">
-        <v>150000</v>
-      </c>
+        <v>625</v>
+      </c>
+      <c r="B6" s="55"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>533</v>
-      </c>
-      <c r="B7" s="55"/>
+        <v>626</v>
+      </c>
+      <c r="B7" s="55">
+        <v>305000</v>
+      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>534</v>
+        <v>627</v>
       </c>
       <c r="B8" s="55">
-        <v>699450</v>
+        <v>1731400</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>432</v>
+        <v>550</v>
       </c>
       <c r="B9" s="55">
-        <v>1748.63</v>
+        <v>4328.5</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>549</v>
-      </c>
-      <c r="B10" s="55"/>
+        <v>642</v>
+      </c>
+      <c r="B10" s="55">
+        <v>25000</v>
+      </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>537</v>
+        <v>630</v>
       </c>
       <c r="B11" s="55"/>
     </row>
@@ -4864,7 +5283,7 @@
   <sheetPr>
     <tabColor rgb="FF16A34A"/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -4874,45 +5293,57 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="53" t="s">
-        <v>180</v>
+        <v>253</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="57" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B3" s="57" t="s">
+        <v>165</v>
+      </c>
+      <c r="C3" s="57" t="s">
+        <v>166</v>
+      </c>
+      <c r="D3" s="57" t="s">
         <v>167</v>
-      </c>
-      <c r="C3" s="57" t="s">
-        <v>168</v>
-      </c>
-      <c r="D3" s="57" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>178</v>
+        <v>251</v>
       </c>
       <c r="B4" s="55">
-        <v>180000</v>
+        <v>1202000</v>
       </c>
       <c r="C4" s="55"/>
       <c r="D4" s="55">
-        <v>180000</v>
+        <v>1202000</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>181</v>
+        <v>254</v>
       </c>
       <c r="B5" s="55">
-        <v>95000</v>
+        <v>225000</v>
       </c>
       <c r="C5" s="55"/>
       <c r="D5" s="55">
-        <v>95000</v>
+        <v>225000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>255</v>
+      </c>
+      <c r="B6" s="55"/>
+      <c r="C6" s="55">
+        <v>100000</v>
+      </c>
+      <c r="D6" s="55">
+        <v>-100000</v>
       </c>
     </row>
   </sheetData>
@@ -4926,7 +5357,7 @@
   <sheetPr>
     <tabColor rgb="FF16A34A"/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -4936,45 +5367,57 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="53" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="57" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B3" s="57" t="s">
+        <v>165</v>
+      </c>
+      <c r="C3" s="57" t="s">
+        <v>166</v>
+      </c>
+      <c r="D3" s="57" t="s">
         <v>167</v>
-      </c>
-      <c r="C3" s="57" t="s">
-        <v>168</v>
-      </c>
-      <c r="D3" s="57" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="B4" s="55"/>
       <c r="C4" s="55">
-        <v>140000</v>
+        <v>475000</v>
       </c>
       <c r="D4" s="55">
-        <v>140000</v>
+        <v>475000</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="B5" s="55"/>
       <c r="C5" s="55">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="D5" s="55">
-        <v>75000</v>
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>181</v>
+      </c>
+      <c r="B6" s="55">
+        <v>100000</v>
+      </c>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55">
+        <v>-100000</v>
       </c>
     </row>
   </sheetData>
@@ -4988,7 +5431,7 @@
   <sheetPr>
     <tabColor rgb="FF16A34A"/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -4998,46 +5441,78 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="53" t="s">
-        <v>550</v>
+        <v>643</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="57" t="s">
-        <v>551</v>
+        <v>644</v>
       </c>
       <c r="B3" s="57" t="s">
-        <v>552</v>
+        <v>645</v>
       </c>
       <c r="C3" s="57" t="s">
-        <v>453</v>
+        <v>572</v>
       </c>
       <c r="D3" s="57" t="s">
-        <v>454</v>
+        <v>573</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B4" t="s">
-        <v>553</v>
+        <v>646</v>
       </c>
       <c r="C4" s="55">
-        <v>250000</v>
-      </c>
-      <c r="D4" s="55"/>
+        <v>-1500000</v>
+      </c>
+      <c r="D4" s="55">
+        <v>-2500000</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B5" t="s">
-        <v>554</v>
+        <v>646</v>
       </c>
       <c r="C5" s="55">
-        <v>500000</v>
-      </c>
-      <c r="D5" s="55"/>
+        <v>-1000000</v>
+      </c>
+      <c r="D5" s="55">
+        <v>-1200000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>264</v>
+      </c>
+      <c r="B6" t="s">
+        <v>646</v>
+      </c>
+      <c r="C6" s="55">
+        <v>115000</v>
+      </c>
+      <c r="D6" s="55">
+        <v>85000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>265</v>
+      </c>
+      <c r="B7" t="s">
+        <v>646</v>
+      </c>
+      <c r="C7" s="55">
+        <v>74000</v>
+      </c>
+      <c r="D7" s="55">
+        <v>115000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5050,7 +5525,7 @@
   <sheetPr>
     <tabColor rgb="FF1E40AF"/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L92"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -5062,820 +5537,2376 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="C1" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="D1" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="E1" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="F1" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="G1" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="H1" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="I1" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="J1" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="K1" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="L1" s="18" t="s">
         <v>167</v>
-      </c>
-      <c r="K1" s="18" t="s">
-        <v>168</v>
-      </c>
-      <c r="L1" s="18" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="2" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20">
-        <v>50000</v>
-      </c>
-      <c r="G2" s="20"/>
+      <c r="E2" s="20">
+        <v>50000000</v>
+      </c>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20">
+        <v>50000000</v>
+      </c>
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
-      <c r="J2" s="20">
-        <v>50000</v>
-      </c>
-      <c r="K2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20">
+        <v>51000000</v>
+      </c>
       <c r="L2" s="20">
-        <v>50000</v>
+        <v>-51000000</v>
       </c>
     </row>
     <row r="3" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="C3" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="B3" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>174</v>
-      </c>
       <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20">
-        <v>250000</v>
-      </c>
-      <c r="G3" s="20"/>
+      <c r="E3" s="20">
+        <v>2532000</v>
+      </c>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20">
+        <v>2532000</v>
+      </c>
       <c r="H3" s="20"/>
       <c r="I3" s="20"/>
-      <c r="J3" s="20">
-        <v>250000</v>
-      </c>
-      <c r="K3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20">
+        <v>2532000</v>
+      </c>
       <c r="L3" s="20">
-        <v>250000</v>
+        <v>-2532000</v>
       </c>
     </row>
     <row r="4" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="C4" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="B4" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>177</v>
-      </c>
       <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20">
-        <v>500000</v>
-      </c>
-      <c r="G4" s="20"/>
+      <c r="E4" s="20">
+        <v>2500000</v>
+      </c>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20">
+        <v>2500000</v>
+      </c>
       <c r="H4" s="20"/>
       <c r="I4" s="20"/>
-      <c r="J4" s="20">
-        <v>500000</v>
-      </c>
-      <c r="K4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20">
+        <v>1500000</v>
+      </c>
       <c r="L4" s="20">
-        <v>500000</v>
+        <v>-1500000</v>
       </c>
     </row>
     <row r="5" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20">
-        <v>180000</v>
-      </c>
-      <c r="G5" s="20"/>
+      <c r="E5" s="20">
+        <v>1200000</v>
+      </c>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20">
+        <v>1200000</v>
+      </c>
       <c r="H5" s="20"/>
       <c r="I5" s="20"/>
-      <c r="J5" s="20">
-        <v>180000</v>
-      </c>
-      <c r="K5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20">
+        <v>1000000</v>
+      </c>
       <c r="L5" s="20">
-        <v>180000</v>
+        <v>-1000000</v>
       </c>
     </row>
     <row r="6" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B6" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="C6" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="C6" s="19" t="s">
-        <v>180</v>
-      </c>
       <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20">
-        <v>95000</v>
-      </c>
-      <c r="G6" s="20"/>
+      <c r="E6" s="20">
+        <v>125000</v>
+      </c>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20">
+        <v>125000</v>
+      </c>
       <c r="H6" s="20"/>
       <c r="I6" s="20"/>
-      <c r="J6" s="20">
-        <v>95000</v>
-      </c>
-      <c r="K6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20">
+        <v>475000</v>
+      </c>
       <c r="L6" s="20">
-        <v>95000</v>
+        <v>-475000</v>
       </c>
     </row>
     <row r="7" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20">
-        <v>45000</v>
-      </c>
-      <c r="G7" s="20"/>
+      <c r="E7" s="20">
+        <v>55000</v>
+      </c>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20">
+        <v>55000</v>
+      </c>
       <c r="H7" s="20"/>
       <c r="I7" s="20"/>
-      <c r="J7" s="20">
-        <v>45000</v>
-      </c>
-      <c r="K7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20">
+        <v>100000</v>
+      </c>
       <c r="L7" s="20">
-        <v>45000</v>
+        <v>-100000</v>
       </c>
     </row>
     <row r="8" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="D8" s="20"/>
       <c r="E8" s="20"/>
-      <c r="F8" s="20">
-        <v>320000</v>
-      </c>
+      <c r="F8" s="20"/>
       <c r="G8" s="20"/>
       <c r="H8" s="20"/>
       <c r="I8" s="20"/>
       <c r="J8" s="20">
-        <v>320000</v>
+        <v>100000</v>
       </c>
       <c r="K8" s="20"/>
       <c r="L8" s="20">
-        <v>320000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="9" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20">
-        <v>2500000</v>
-      </c>
-      <c r="G9" s="20"/>
+      <c r="E9" s="20">
+        <v>115000</v>
+      </c>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20">
+        <v>115000</v>
+      </c>
       <c r="H9" s="20"/>
       <c r="I9" s="20"/>
-      <c r="J9" s="20">
-        <v>2500000</v>
-      </c>
-      <c r="K9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20">
+        <v>150000</v>
+      </c>
       <c r="L9" s="20">
-        <v>2500000</v>
+        <v>-150000</v>
       </c>
     </row>
     <row r="10" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20">
-        <v>1200000</v>
-      </c>
-      <c r="G10" s="20"/>
+      <c r="E10" s="20">
+        <v>115000</v>
+      </c>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20">
+        <v>115000</v>
+      </c>
       <c r="H10" s="20"/>
       <c r="I10" s="20"/>
-      <c r="J10" s="20">
-        <v>1200000</v>
-      </c>
-      <c r="K10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="20">
+        <v>247349</v>
+      </c>
       <c r="L10" s="20">
-        <v>1200000</v>
+        <v>-247349</v>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>193</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="C11" s="19"/>
       <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
+      <c r="E11" s="20">
+        <v>25000</v>
+      </c>
       <c r="F11" s="20"/>
       <c r="G11" s="20">
-        <v>500000</v>
+        <v>25000</v>
       </c>
       <c r="H11" s="20"/>
       <c r="I11" s="20"/>
       <c r="J11" s="20"/>
       <c r="K11" s="20">
-        <v>500000</v>
+        <v>25000</v>
       </c>
       <c r="L11" s="20">
-        <v>-500000</v>
+        <v>-25000</v>
       </c>
     </row>
     <row r="12" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>195</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="C12" s="19"/>
       <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20">
-        <v>15000</v>
-      </c>
-      <c r="G12" s="20"/>
+      <c r="E12" s="20">
+        <v>75000</v>
+      </c>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20">
+        <v>75000</v>
+      </c>
       <c r="H12" s="20"/>
       <c r="I12" s="20"/>
-      <c r="J12" s="20">
-        <v>15000</v>
-      </c>
-      <c r="K12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20">
+        <v>45000</v>
+      </c>
       <c r="L12" s="20">
-        <v>15000</v>
+        <v>-45000</v>
       </c>
     </row>
     <row r="13" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>199</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="C13" s="19"/>
       <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
+      <c r="E13" s="20">
+        <v>115000</v>
+      </c>
       <c r="F13" s="20"/>
       <c r="G13" s="20">
-        <v>140000</v>
+        <v>115000</v>
       </c>
       <c r="H13" s="20"/>
       <c r="I13" s="20"/>
       <c r="J13" s="20"/>
       <c r="K13" s="20">
-        <v>140000</v>
+        <v>95000</v>
       </c>
       <c r="L13" s="20">
-        <v>-140000</v>
+        <v>-95000</v>
       </c>
     </row>
     <row r="14" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
+      <c r="E14" s="20">
+        <v>10000</v>
+      </c>
       <c r="F14" s="20"/>
       <c r="G14" s="20">
-        <v>75000</v>
+        <v>10000</v>
       </c>
       <c r="H14" s="20"/>
       <c r="I14" s="20"/>
       <c r="J14" s="20"/>
       <c r="K14" s="20">
-        <v>75000</v>
+        <v>20000</v>
       </c>
       <c r="L14" s="20">
-        <v>-75000</v>
+        <v>-20000</v>
       </c>
     </row>
     <row r="15" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
+      <c r="E15" s="20">
+        <v>15000</v>
+      </c>
       <c r="F15" s="20"/>
       <c r="G15" s="20">
-        <v>35000</v>
+        <v>15000</v>
       </c>
       <c r="H15" s="20"/>
       <c r="I15" s="20"/>
       <c r="J15" s="20"/>
       <c r="K15" s="20">
-        <v>35000</v>
+        <v>30000</v>
       </c>
       <c r="L15" s="20">
-        <v>-35000</v>
+        <v>-30000</v>
       </c>
     </row>
     <row r="16" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D16" s="20"/>
       <c r="E16" s="20"/>
       <c r="F16" s="20"/>
-      <c r="G16" s="20">
-        <v>8500</v>
-      </c>
+      <c r="G16" s="20"/>
       <c r="H16" s="20"/>
       <c r="I16" s="20"/>
       <c r="J16" s="20"/>
       <c r="K16" s="20">
-        <v>8500</v>
+        <v>10000</v>
       </c>
       <c r="L16" s="20">
-        <v>-8500</v>
+        <v>-10000</v>
       </c>
     </row>
     <row r="17" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
+      <c r="E17" s="20">
+        <v>10000</v>
+      </c>
       <c r="F17" s="20"/>
       <c r="G17" s="20">
-        <v>800000</v>
+        <v>10000</v>
       </c>
       <c r="H17" s="20"/>
       <c r="I17" s="20"/>
       <c r="J17" s="20"/>
       <c r="K17" s="20">
-        <v>800000</v>
+        <v>25000</v>
       </c>
       <c r="L17" s="20">
-        <v>-800000</v>
+        <v>-25000</v>
       </c>
     </row>
     <row r="18" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
+      <c r="E18" s="20">
+        <v>25000</v>
+      </c>
       <c r="F18" s="20"/>
       <c r="G18" s="20">
-        <v>2000000</v>
+        <v>25000</v>
       </c>
       <c r="H18" s="20"/>
       <c r="I18" s="20"/>
       <c r="J18" s="20"/>
       <c r="K18" s="20">
-        <v>2000000</v>
+        <v>25000</v>
       </c>
       <c r="L18" s="20">
-        <v>-2000000</v>
+        <v>-25000</v>
       </c>
     </row>
     <row r="19" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
+      <c r="E19" s="20">
+        <v>5000</v>
+      </c>
       <c r="F19" s="20"/>
       <c r="G19" s="20">
-        <v>500000</v>
+        <v>5000</v>
       </c>
       <c r="H19" s="20"/>
       <c r="I19" s="20"/>
       <c r="J19" s="20"/>
       <c r="K19" s="20">
-        <v>500000</v>
+        <v>5000</v>
       </c>
       <c r="L19" s="20">
-        <v>-500000</v>
+        <v>-5000</v>
       </c>
     </row>
     <row r="20" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
+      <c r="E20" s="20">
+        <v>10000</v>
+      </c>
       <c r="F20" s="20"/>
       <c r="G20" s="20">
-        <v>200000</v>
+        <v>10000</v>
       </c>
       <c r="H20" s="20"/>
       <c r="I20" s="20"/>
       <c r="J20" s="20"/>
       <c r="K20" s="20">
-        <v>200000</v>
+        <v>10000</v>
       </c>
       <c r="L20" s="20">
-        <v>-200000</v>
+        <v>-10000</v>
       </c>
     </row>
     <row r="21" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
+      <c r="E21" s="20">
+        <v>15000</v>
+      </c>
       <c r="F21" s="20"/>
       <c r="G21" s="20">
-        <v>3500000</v>
+        <v>15000</v>
       </c>
       <c r="H21" s="20"/>
       <c r="I21" s="20"/>
       <c r="J21" s="20"/>
       <c r="K21" s="20">
-        <v>3500000</v>
+        <v>30000</v>
       </c>
       <c r="L21" s="20">
-        <v>-3500000</v>
+        <v>-30000</v>
       </c>
     </row>
     <row r="22" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
+      <c r="E22" s="20">
+        <v>5000</v>
+      </c>
       <c r="F22" s="20"/>
       <c r="G22" s="20">
-        <v>320000</v>
+        <v>5000</v>
       </c>
       <c r="H22" s="20"/>
       <c r="I22" s="20"/>
       <c r="J22" s="20"/>
       <c r="K22" s="20">
-        <v>320000</v>
+        <v>5000</v>
       </c>
       <c r="L22" s="20">
-        <v>-320000</v>
+        <v>-5000</v>
       </c>
     </row>
     <row r="23" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20">
-        <v>2100000</v>
-      </c>
-      <c r="G23" s="20"/>
+      <c r="E23" s="20">
+        <v>10000</v>
+      </c>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20">
+        <v>10000</v>
+      </c>
       <c r="H23" s="20"/>
       <c r="I23" s="20"/>
-      <c r="J23" s="20">
-        <v>2100000</v>
-      </c>
-      <c r="K23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20">
+        <v>10000</v>
+      </c>
       <c r="L23" s="20">
-        <v>2100000</v>
+        <v>-10000</v>
       </c>
     </row>
     <row r="24" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20">
-        <v>280000</v>
-      </c>
-      <c r="G24" s="20"/>
+      <c r="E24" s="20">
+        <v>15000</v>
+      </c>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20">
+        <v>15000</v>
+      </c>
       <c r="H24" s="20"/>
       <c r="I24" s="20"/>
-      <c r="J24" s="20">
-        <v>280000</v>
-      </c>
-      <c r="K24" s="20"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20">
+        <v>30000</v>
+      </c>
       <c r="L24" s="20">
-        <v>280000</v>
+        <v>-30000</v>
       </c>
     </row>
     <row r="25" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="19" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20">
-        <v>25200</v>
-      </c>
-      <c r="G25" s="20"/>
+      <c r="E25" s="20">
+        <v>55000</v>
+      </c>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20">
+        <v>55000</v>
+      </c>
       <c r="H25" s="20"/>
       <c r="I25" s="20"/>
-      <c r="J25" s="20">
-        <v>25200</v>
-      </c>
-      <c r="K25" s="20"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="20">
+        <v>252243</v>
+      </c>
       <c r="L25" s="20">
-        <v>25200</v>
+        <v>-252243</v>
       </c>
     </row>
     <row r="26" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="19" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="D26" s="20"/>
+        <v>211</v>
+      </c>
+      <c r="D26" s="20">
+        <v>37190767</v>
+      </c>
       <c r="E26" s="20"/>
       <c r="F26" s="20">
-        <v>120000</v>
+        <v>37190767</v>
       </c>
       <c r="G26" s="20"/>
       <c r="H26" s="20"/>
       <c r="I26" s="20"/>
       <c r="J26" s="20">
-        <v>120000</v>
+        <v>37190767</v>
       </c>
       <c r="K26" s="20"/>
       <c r="L26" s="20">
-        <v>120000</v>
+        <v>37190767</v>
       </c>
     </row>
     <row r="27" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="19" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>230</v>
-      </c>
-      <c r="D27" s="20"/>
+        <v>215</v>
+      </c>
+      <c r="D27" s="20">
+        <v>5500000</v>
+      </c>
       <c r="E27" s="20"/>
       <c r="F27" s="20">
-        <v>18000</v>
+        <v>5500000</v>
       </c>
       <c r="G27" s="20"/>
       <c r="H27" s="20"/>
       <c r="I27" s="20"/>
       <c r="J27" s="20">
-        <v>18000</v>
+        <v>5500000</v>
       </c>
       <c r="K27" s="20"/>
       <c r="L27" s="20">
-        <v>18000</v>
+        <v>5500000</v>
       </c>
     </row>
     <row r="28" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="19" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>233</v>
-      </c>
-      <c r="D28" s="20"/>
+        <v>218</v>
+      </c>
+      <c r="D28" s="20">
+        <v>1900000</v>
+      </c>
       <c r="E28" s="20"/>
       <c r="F28" s="20">
-        <v>72000</v>
+        <v>1900000</v>
       </c>
       <c r="G28" s="20"/>
       <c r="H28" s="20"/>
       <c r="I28" s="20"/>
       <c r="J28" s="20">
-        <v>72000</v>
+        <v>1900000</v>
       </c>
       <c r="K28" s="20"/>
       <c r="L28" s="20">
-        <v>72000</v>
+        <v>1900000</v>
       </c>
     </row>
     <row r="29" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>234</v>
-      </c>
-      <c r="D29" s="20"/>
+        <v>221</v>
+      </c>
+      <c r="D29" s="20">
+        <v>1700000</v>
+      </c>
       <c r="E29" s="20"/>
       <c r="F29" s="20">
-        <v>35000</v>
+        <v>1700000</v>
       </c>
       <c r="G29" s="20"/>
       <c r="H29" s="20"/>
       <c r="I29" s="20"/>
       <c r="J29" s="20">
-        <v>35000</v>
+        <v>1700000</v>
       </c>
       <c r="K29" s="20"/>
       <c r="L29" s="20">
-        <v>35000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="30" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="D30" s="20"/>
+        <v>222</v>
+      </c>
+      <c r="D30" s="20">
+        <v>2200000</v>
+      </c>
       <c r="E30" s="20"/>
       <c r="F30" s="20">
-        <v>409300</v>
+        <v>2200000</v>
       </c>
       <c r="G30" s="20"/>
       <c r="H30" s="20"/>
       <c r="I30" s="20"/>
       <c r="J30" s="20">
-        <v>409300</v>
+        <v>2200000</v>
       </c>
       <c r="K30" s="20"/>
       <c r="L30" s="20">
-        <v>409300</v>
+        <v>2200000</v>
       </c>
     </row>
     <row r="31" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="D31" s="20"/>
+        <v>226</v>
+      </c>
+      <c r="D31" s="20">
+        <v>165000</v>
+      </c>
       <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20">
-        <v>136000</v>
-      </c>
+      <c r="F31" s="20">
+        <v>165000</v>
+      </c>
+      <c r="G31" s="20"/>
       <c r="H31" s="20"/>
       <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
-      <c r="K31" s="20">
-        <v>136000</v>
-      </c>
+      <c r="J31" s="20">
+        <v>165000</v>
+      </c>
+      <c r="K31" s="20"/>
       <c r="L31" s="20">
-        <v>-136000</v>
+        <v>165000</v>
+      </c>
+    </row>
+    <row r="32" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="D32" s="20">
+        <v>6000000</v>
+      </c>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20">
+        <v>6000000</v>
+      </c>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20">
+        <v>6000000</v>
+      </c>
+      <c r="K32" s="20"/>
+      <c r="L32" s="20">
+        <v>6000000</v>
+      </c>
+    </row>
+    <row r="33" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="C33" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="D33" s="20">
+        <v>2800000</v>
+      </c>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20">
+        <v>2800000</v>
+      </c>
+      <c r="G33" s="20"/>
+      <c r="H33" s="20"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="20">
+        <v>2800000</v>
+      </c>
+      <c r="K33" s="20"/>
+      <c r="L33" s="20">
+        <v>2800000</v>
+      </c>
+    </row>
+    <row r="34" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="C34" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="20">
+        <v>1010000</v>
+      </c>
+      <c r="K34" s="20"/>
+      <c r="L34" s="20">
+        <v>1010000</v>
+      </c>
+    </row>
+    <row r="35" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="B35" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="C35" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20">
+        <v>2380767</v>
+      </c>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20">
+        <v>2380767</v>
+      </c>
+      <c r="H35" s="20"/>
+      <c r="I35" s="20"/>
+      <c r="J35" s="20"/>
+      <c r="K35" s="20">
+        <v>3288274</v>
+      </c>
+      <c r="L35" s="20">
+        <v>-3288274</v>
+      </c>
+    </row>
+    <row r="36" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="B36" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="C36" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
+      <c r="H36" s="20"/>
+      <c r="I36" s="20"/>
+      <c r="J36" s="20">
+        <v>500000</v>
+      </c>
+      <c r="K36" s="20"/>
+      <c r="L36" s="20">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="37" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="C37" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="20"/>
+      <c r="H37" s="20"/>
+      <c r="I37" s="20"/>
+      <c r="J37" s="20">
+        <v>1200000</v>
+      </c>
+      <c r="K37" s="20"/>
+      <c r="L37" s="20">
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="38" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="B38" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="C38" s="19"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="20"/>
+      <c r="H38" s="20"/>
+      <c r="I38" s="20"/>
+      <c r="J38" s="20"/>
+      <c r="K38" s="20">
+        <v>200000</v>
+      </c>
+      <c r="L38" s="20">
+        <v>-200000</v>
+      </c>
+    </row>
+    <row r="39" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" s="19" t="s">
+        <v>243</v>
+      </c>
+      <c r="B39" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="C39" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="D39" s="20">
+        <v>225000</v>
+      </c>
+      <c r="E39" s="20"/>
+      <c r="F39" s="20">
+        <v>225000</v>
+      </c>
+      <c r="G39" s="20"/>
+      <c r="H39" s="20"/>
+      <c r="I39" s="20"/>
+      <c r="J39" s="20">
+        <v>275000</v>
+      </c>
+      <c r="K39" s="20"/>
+      <c r="L39" s="20">
+        <v>275000</v>
+      </c>
+    </row>
+    <row r="40" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="B40" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="C40" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="D40" s="20">
+        <v>20000</v>
+      </c>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20">
+        <v>20000</v>
+      </c>
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="20"/>
+      <c r="J40" s="20">
+        <v>50000</v>
+      </c>
+      <c r="K40" s="20"/>
+      <c r="L40" s="20">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="41" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="B41" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="C41" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="D41" s="20">
+        <v>75000</v>
+      </c>
+      <c r="E41" s="20"/>
+      <c r="F41" s="20">
+        <v>75000</v>
+      </c>
+      <c r="G41" s="20"/>
+      <c r="H41" s="20"/>
+      <c r="I41" s="20"/>
+      <c r="J41" s="20">
+        <v>25000</v>
+      </c>
+      <c r="K41" s="20"/>
+      <c r="L41" s="20">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="42" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="B42" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="C42" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="D42" s="20">
+        <v>1302000</v>
+      </c>
+      <c r="E42" s="20"/>
+      <c r="F42" s="20">
+        <v>1302000</v>
+      </c>
+      <c r="G42" s="20"/>
+      <c r="H42" s="20"/>
+      <c r="I42" s="20"/>
+      <c r="J42" s="20">
+        <v>1202000</v>
+      </c>
+      <c r="K42" s="20"/>
+      <c r="L42" s="20">
+        <v>1202000</v>
+      </c>
+    </row>
+    <row r="43" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A43" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="B43" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="C43" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="D43" s="20">
+        <v>75000</v>
+      </c>
+      <c r="E43" s="20"/>
+      <c r="F43" s="20">
+        <v>75000</v>
+      </c>
+      <c r="G43" s="20"/>
+      <c r="H43" s="20"/>
+      <c r="I43" s="20"/>
+      <c r="J43" s="20">
+        <v>225000</v>
+      </c>
+      <c r="K43" s="20"/>
+      <c r="L43" s="20">
+        <v>225000</v>
+      </c>
+    </row>
+    <row r="44" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="B44" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="C44" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="D44" s="20"/>
+      <c r="E44" s="20"/>
+      <c r="F44" s="20"/>
+      <c r="G44" s="20"/>
+      <c r="H44" s="20"/>
+      <c r="I44" s="20"/>
+      <c r="J44" s="20"/>
+      <c r="K44" s="20">
+        <v>100000</v>
+      </c>
+      <c r="L44" s="20">
+        <v>-100000</v>
+      </c>
+    </row>
+    <row r="45" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="B45" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="C45" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="D45" s="20"/>
+      <c r="E45" s="20"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="20"/>
+      <c r="H45" s="20"/>
+      <c r="I45" s="20"/>
+      <c r="J45" s="20"/>
+      <c r="K45" s="20">
+        <v>100000</v>
+      </c>
+      <c r="L45" s="20">
+        <v>-100000</v>
+      </c>
+    </row>
+    <row r="46" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="B46" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="C46" s="19"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="20"/>
+      <c r="H46" s="20"/>
+      <c r="I46" s="20"/>
+      <c r="J46" s="20">
+        <v>50000</v>
+      </c>
+      <c r="K46" s="20"/>
+      <c r="L46" s="20">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="47" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A47" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="B47" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="C47" s="19"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="20"/>
+      <c r="H47" s="20"/>
+      <c r="I47" s="20"/>
+      <c r="J47" s="20">
+        <v>50000</v>
+      </c>
+      <c r="K47" s="20"/>
+      <c r="L47" s="20">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="48" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="B48" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="C48" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="D48" s="20">
+        <v>10000</v>
+      </c>
+      <c r="E48" s="20"/>
+      <c r="F48" s="20">
+        <v>10000</v>
+      </c>
+      <c r="G48" s="20"/>
+      <c r="H48" s="20"/>
+      <c r="I48" s="20"/>
+      <c r="J48" s="20">
+        <v>22000</v>
+      </c>
+      <c r="K48" s="20"/>
+      <c r="L48" s="20">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="49" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="B49" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="C49" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="D49" s="20">
+        <v>85000</v>
+      </c>
+      <c r="E49" s="20"/>
+      <c r="F49" s="20">
+        <v>85000</v>
+      </c>
+      <c r="G49" s="20"/>
+      <c r="H49" s="20"/>
+      <c r="I49" s="20"/>
+      <c r="J49" s="20">
+        <v>115000</v>
+      </c>
+      <c r="K49" s="20"/>
+      <c r="L49" s="20">
+        <v>115000</v>
+      </c>
+    </row>
+    <row r="50" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="B50" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="C50" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="D50" s="20">
+        <v>115000</v>
+      </c>
+      <c r="E50" s="20"/>
+      <c r="F50" s="20">
+        <v>115000</v>
+      </c>
+      <c r="G50" s="20"/>
+      <c r="H50" s="20"/>
+      <c r="I50" s="20"/>
+      <c r="J50" s="20">
+        <v>74000</v>
+      </c>
+      <c r="K50" s="20"/>
+      <c r="L50" s="20">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="51" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="B51" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="C51" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="D51" s="20">
+        <v>25000</v>
+      </c>
+      <c r="E51" s="20"/>
+      <c r="F51" s="20">
+        <v>25000</v>
+      </c>
+      <c r="G51" s="20"/>
+      <c r="H51" s="20"/>
+      <c r="I51" s="20"/>
+      <c r="J51" s="20">
+        <v>25000</v>
+      </c>
+      <c r="K51" s="20"/>
+      <c r="L51" s="20">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="52" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="B52" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="C52" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="D52" s="20">
+        <v>25000</v>
+      </c>
+      <c r="E52" s="20"/>
+      <c r="F52" s="20">
+        <v>25000</v>
+      </c>
+      <c r="G52" s="20"/>
+      <c r="H52" s="20"/>
+      <c r="I52" s="20"/>
+      <c r="J52" s="20">
+        <v>25000</v>
+      </c>
+      <c r="K52" s="20"/>
+      <c r="L52" s="20">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="53" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="B53" s="19" t="s">
+        <v>273</v>
+      </c>
+      <c r="C53" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="D53" s="20"/>
+      <c r="E53" s="20"/>
+      <c r="F53" s="20"/>
+      <c r="G53" s="20"/>
+      <c r="H53" s="20"/>
+      <c r="I53" s="20"/>
+      <c r="J53" s="20">
+        <v>10000</v>
+      </c>
+      <c r="K53" s="20"/>
+      <c r="L53" s="20">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="54" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" s="19" t="s">
+        <v>275</v>
+      </c>
+      <c r="B54" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="C54" s="19" t="s">
+        <v>275</v>
+      </c>
+      <c r="D54" s="20"/>
+      <c r="E54" s="20"/>
+      <c r="F54" s="20"/>
+      <c r="G54" s="20"/>
+      <c r="H54" s="20"/>
+      <c r="I54" s="20"/>
+      <c r="J54" s="20"/>
+      <c r="K54" s="20">
+        <v>9000000</v>
+      </c>
+      <c r="L54" s="20">
+        <v>-9000000</v>
+      </c>
+    </row>
+    <row r="55" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A55" s="19" t="s">
+        <v>277</v>
+      </c>
+      <c r="B55" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="C55" s="19" t="s">
+        <v>277</v>
+      </c>
+      <c r="D55" s="20"/>
+      <c r="E55" s="20"/>
+      <c r="F55" s="20"/>
+      <c r="G55" s="20"/>
+      <c r="H55" s="20"/>
+      <c r="I55" s="20"/>
+      <c r="J55" s="20"/>
+      <c r="K55" s="20">
+        <v>1500000</v>
+      </c>
+      <c r="L55" s="20">
+        <v>-1500000</v>
+      </c>
+    </row>
+    <row r="56" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A56" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="B56" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="C56" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="D56" s="20"/>
+      <c r="E56" s="20"/>
+      <c r="F56" s="20"/>
+      <c r="G56" s="20"/>
+      <c r="H56" s="20"/>
+      <c r="I56" s="20"/>
+      <c r="J56" s="20">
+        <v>6000000</v>
+      </c>
+      <c r="K56" s="20"/>
+      <c r="L56" s="20">
+        <v>6000000</v>
+      </c>
+    </row>
+    <row r="57" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A57" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="B57" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="C57" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="D57" s="20"/>
+      <c r="E57" s="20"/>
+      <c r="F57" s="20"/>
+      <c r="G57" s="20"/>
+      <c r="H57" s="20"/>
+      <c r="I57" s="20"/>
+      <c r="J57" s="20">
+        <v>500000</v>
+      </c>
+      <c r="K57" s="20"/>
+      <c r="L57" s="20">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="58" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A58" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="B58" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="C58" s="19" t="s">
+        <v>287</v>
+      </c>
+      <c r="D58" s="20"/>
+      <c r="E58" s="20"/>
+      <c r="F58" s="20"/>
+      <c r="G58" s="20"/>
+      <c r="H58" s="20"/>
+      <c r="I58" s="20"/>
+      <c r="J58" s="20">
+        <v>100000</v>
+      </c>
+      <c r="K58" s="20"/>
+      <c r="L58" s="20">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="59" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A59" s="19" t="s">
+        <v>288</v>
+      </c>
+      <c r="B59" s="19" t="s">
+        <v>289</v>
+      </c>
+      <c r="C59" s="19" t="s">
+        <v>288</v>
+      </c>
+      <c r="D59" s="20"/>
+      <c r="E59" s="20"/>
+      <c r="F59" s="20"/>
+      <c r="G59" s="20"/>
+      <c r="H59" s="20"/>
+      <c r="I59" s="20"/>
+      <c r="J59" s="20"/>
+      <c r="K59" s="20">
+        <v>2000</v>
+      </c>
+      <c r="L59" s="20">
+        <v>-2000</v>
+      </c>
+    </row>
+    <row r="60" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A60" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="B60" s="19" t="s">
+        <v>291</v>
+      </c>
+      <c r="C60" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="D60" s="20"/>
+      <c r="E60" s="20"/>
+      <c r="F60" s="20"/>
+      <c r="G60" s="20"/>
+      <c r="H60" s="20"/>
+      <c r="I60" s="20"/>
+      <c r="J60" s="20"/>
+      <c r="K60" s="20">
+        <v>50000</v>
+      </c>
+      <c r="L60" s="20">
+        <v>-50000</v>
+      </c>
+    </row>
+    <row r="61" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A61" s="19" t="s">
+        <v>292</v>
+      </c>
+      <c r="B61" s="19" t="s">
+        <v>291</v>
+      </c>
+      <c r="C61" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="D61" s="20"/>
+      <c r="E61" s="20"/>
+      <c r="F61" s="20"/>
+      <c r="G61" s="20"/>
+      <c r="H61" s="20"/>
+      <c r="I61" s="20"/>
+      <c r="J61" s="20"/>
+      <c r="K61" s="20">
+        <v>5000</v>
+      </c>
+      <c r="L61" s="20">
+        <v>-5000</v>
+      </c>
+    </row>
+    <row r="62" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A62" s="19" t="s">
+        <v>294</v>
+      </c>
+      <c r="B62" s="19" t="s">
+        <v>295</v>
+      </c>
+      <c r="C62" s="19" t="s">
+        <v>294</v>
+      </c>
+      <c r="D62" s="20"/>
+      <c r="E62" s="20"/>
+      <c r="F62" s="20"/>
+      <c r="G62" s="20"/>
+      <c r="H62" s="20"/>
+      <c r="I62" s="20"/>
+      <c r="J62" s="20"/>
+      <c r="K62" s="20">
+        <v>5000</v>
+      </c>
+      <c r="L62" s="20">
+        <v>-5000</v>
+      </c>
+    </row>
+    <row r="63" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A63" s="19" t="s">
+        <v>296</v>
+      </c>
+      <c r="B63" s="19" t="s">
+        <v>297</v>
+      </c>
+      <c r="C63" s="19" t="s">
+        <v>296</v>
+      </c>
+      <c r="D63" s="20"/>
+      <c r="E63" s="20"/>
+      <c r="F63" s="20"/>
+      <c r="G63" s="20"/>
+      <c r="H63" s="20"/>
+      <c r="I63" s="20"/>
+      <c r="J63" s="20"/>
+      <c r="K63" s="20">
+        <v>10000</v>
+      </c>
+      <c r="L63" s="20">
+        <v>-10000</v>
+      </c>
+    </row>
+    <row r="64" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A64" s="19" t="s">
+        <v>298</v>
+      </c>
+      <c r="B64" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="C64" s="19" t="s">
+        <v>300</v>
+      </c>
+      <c r="D64" s="20"/>
+      <c r="E64" s="20"/>
+      <c r="F64" s="20"/>
+      <c r="G64" s="20"/>
+      <c r="H64" s="20"/>
+      <c r="I64" s="20"/>
+      <c r="J64" s="20">
+        <v>500000</v>
+      </c>
+      <c r="K64" s="20"/>
+      <c r="L64" s="20">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="65" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A65" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="B65" s="19" t="s">
+        <v>302</v>
+      </c>
+      <c r="C65" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="D65" s="20"/>
+      <c r="E65" s="20"/>
+      <c r="F65" s="20"/>
+      <c r="G65" s="20"/>
+      <c r="H65" s="20"/>
+      <c r="I65" s="20"/>
+      <c r="J65" s="20">
+        <v>100000</v>
+      </c>
+      <c r="K65" s="20"/>
+      <c r="L65" s="20">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="66" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A66" s="19" t="s">
+        <v>304</v>
+      </c>
+      <c r="B66" s="19" t="s">
+        <v>305</v>
+      </c>
+      <c r="C66" s="19" t="s">
+        <v>306</v>
+      </c>
+      <c r="D66" s="20"/>
+      <c r="E66" s="20"/>
+      <c r="F66" s="20"/>
+      <c r="G66" s="20"/>
+      <c r="H66" s="20"/>
+      <c r="I66" s="20"/>
+      <c r="J66" s="20">
+        <v>100000</v>
+      </c>
+      <c r="K66" s="20"/>
+      <c r="L66" s="20">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="67" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A67" s="19" t="s">
+        <v>307</v>
+      </c>
+      <c r="B67" s="19" t="s">
+        <v>308</v>
+      </c>
+      <c r="C67" s="19" t="s">
+        <v>307</v>
+      </c>
+      <c r="D67" s="20"/>
+      <c r="E67" s="20"/>
+      <c r="F67" s="20"/>
+      <c r="G67" s="20"/>
+      <c r="H67" s="20"/>
+      <c r="I67" s="20"/>
+      <c r="J67" s="20">
+        <v>132349</v>
+      </c>
+      <c r="K67" s="20"/>
+      <c r="L67" s="20">
+        <v>132349</v>
+      </c>
+    </row>
+    <row r="68" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A68" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="B68" s="19" t="s">
+        <v>302</v>
+      </c>
+      <c r="C68" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="D68" s="20"/>
+      <c r="E68" s="20"/>
+      <c r="F68" s="20"/>
+      <c r="G68" s="20"/>
+      <c r="H68" s="20"/>
+      <c r="I68" s="20"/>
+      <c r="J68" s="20">
+        <v>20000</v>
+      </c>
+      <c r="K68" s="20"/>
+      <c r="L68" s="20">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="69" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A69" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="B69" s="19" t="s">
+        <v>302</v>
+      </c>
+      <c r="C69" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="D69" s="20"/>
+      <c r="E69" s="20"/>
+      <c r="F69" s="20"/>
+      <c r="G69" s="20"/>
+      <c r="H69" s="20"/>
+      <c r="I69" s="20"/>
+      <c r="J69" s="20">
+        <v>50000</v>
+      </c>
+      <c r="K69" s="20"/>
+      <c r="L69" s="20">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="70" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A70" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="B70" s="19" t="s">
+        <v>312</v>
+      </c>
+      <c r="C70" s="19" t="s">
+        <v>313</v>
+      </c>
+      <c r="D70" s="20"/>
+      <c r="E70" s="20"/>
+      <c r="F70" s="20"/>
+      <c r="G70" s="20"/>
+      <c r="H70" s="20"/>
+      <c r="I70" s="20"/>
+      <c r="J70" s="20">
+        <v>250000</v>
+      </c>
+      <c r="K70" s="20"/>
+      <c r="L70" s="20">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="71" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A71" s="19" t="s">
+        <v>314</v>
+      </c>
+      <c r="B71" s="19" t="s">
+        <v>315</v>
+      </c>
+      <c r="C71" s="19" t="s">
+        <v>314</v>
+      </c>
+      <c r="D71" s="20"/>
+      <c r="E71" s="20"/>
+      <c r="F71" s="20"/>
+      <c r="G71" s="20"/>
+      <c r="H71" s="20"/>
+      <c r="I71" s="20"/>
+      <c r="J71" s="20">
+        <v>10000</v>
+      </c>
+      <c r="K71" s="20"/>
+      <c r="L71" s="20">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="72" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A72" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="B72" s="19" t="s">
+        <v>316</v>
+      </c>
+      <c r="C72" s="19" t="s">
+        <v>317</v>
+      </c>
+      <c r="D72" s="20"/>
+      <c r="E72" s="20"/>
+      <c r="F72" s="20"/>
+      <c r="G72" s="20"/>
+      <c r="H72" s="20"/>
+      <c r="I72" s="20"/>
+      <c r="J72" s="20">
+        <v>907506</v>
+      </c>
+      <c r="K72" s="20"/>
+      <c r="L72" s="20">
+        <v>907506</v>
+      </c>
+    </row>
+    <row r="73" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A73" s="19" t="s">
+        <v>318</v>
+      </c>
+      <c r="B73" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="C73" s="19" t="s">
+        <v>320</v>
+      </c>
+      <c r="D73" s="20"/>
+      <c r="E73" s="20"/>
+      <c r="F73" s="20"/>
+      <c r="G73" s="20"/>
+      <c r="H73" s="20"/>
+      <c r="I73" s="20"/>
+      <c r="J73" s="20">
+        <v>100000</v>
+      </c>
+      <c r="K73" s="20"/>
+      <c r="L73" s="20">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="74" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A74" s="19" t="s">
+        <v>321</v>
+      </c>
+      <c r="B74" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="C74" s="19" t="s">
+        <v>320</v>
+      </c>
+      <c r="D74" s="20"/>
+      <c r="E74" s="20"/>
+      <c r="F74" s="20"/>
+      <c r="G74" s="20"/>
+      <c r="H74" s="20"/>
+      <c r="I74" s="20"/>
+      <c r="J74" s="20">
+        <v>200000</v>
+      </c>
+      <c r="K74" s="20"/>
+      <c r="L74" s="20">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="75" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A75" s="19" t="s">
+        <v>322</v>
+      </c>
+      <c r="B75" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="C75" s="19" t="s">
+        <v>324</v>
+      </c>
+      <c r="D75" s="20"/>
+      <c r="E75" s="20"/>
+      <c r="F75" s="20"/>
+      <c r="G75" s="20"/>
+      <c r="H75" s="20"/>
+      <c r="I75" s="20"/>
+      <c r="J75" s="20">
+        <v>10000</v>
+      </c>
+      <c r="K75" s="20"/>
+      <c r="L75" s="20">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="76" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A76" s="19" t="s">
+        <v>325</v>
+      </c>
+      <c r="B76" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="C76" s="19" t="s">
+        <v>324</v>
+      </c>
+      <c r="D76" s="20"/>
+      <c r="E76" s="20"/>
+      <c r="F76" s="20"/>
+      <c r="G76" s="20"/>
+      <c r="H76" s="20"/>
+      <c r="I76" s="20"/>
+      <c r="J76" s="20">
+        <v>5000</v>
+      </c>
+      <c r="K76" s="20"/>
+      <c r="L76" s="20">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="77" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A77" s="19" t="s">
+        <v>326</v>
+      </c>
+      <c r="B77" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="C77" s="19" t="s">
+        <v>324</v>
+      </c>
+      <c r="D77" s="20"/>
+      <c r="E77" s="20"/>
+      <c r="F77" s="20"/>
+      <c r="G77" s="20"/>
+      <c r="H77" s="20"/>
+      <c r="I77" s="20"/>
+      <c r="J77" s="20">
+        <v>25000</v>
+      </c>
+      <c r="K77" s="20"/>
+      <c r="L77" s="20">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="78" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A78" s="19" t="s">
+        <v>327</v>
+      </c>
+      <c r="B78" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="C78" s="19" t="s">
+        <v>324</v>
+      </c>
+      <c r="D78" s="20"/>
+      <c r="E78" s="20"/>
+      <c r="F78" s="20"/>
+      <c r="G78" s="20"/>
+      <c r="H78" s="20"/>
+      <c r="I78" s="20"/>
+      <c r="J78" s="20">
+        <v>10000</v>
+      </c>
+      <c r="K78" s="20"/>
+      <c r="L78" s="20">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="79" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A79" s="19" t="s">
+        <v>328</v>
+      </c>
+      <c r="B79" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="C79" s="19" t="s">
+        <v>324</v>
+      </c>
+      <c r="D79" s="20"/>
+      <c r="E79" s="20"/>
+      <c r="F79" s="20"/>
+      <c r="G79" s="20"/>
+      <c r="H79" s="20"/>
+      <c r="I79" s="20"/>
+      <c r="J79" s="20">
+        <v>1000</v>
+      </c>
+      <c r="K79" s="20"/>
+      <c r="L79" s="20">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="80" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A80" s="19" t="s">
+        <v>329</v>
+      </c>
+      <c r="B80" s="19" t="s">
+        <v>330</v>
+      </c>
+      <c r="C80" s="19" t="s">
+        <v>329</v>
+      </c>
+      <c r="D80" s="20"/>
+      <c r="E80" s="20"/>
+      <c r="F80" s="20"/>
+      <c r="G80" s="20"/>
+      <c r="H80" s="20"/>
+      <c r="I80" s="20"/>
+      <c r="J80" s="20">
+        <v>252243</v>
+      </c>
+      <c r="K80" s="20"/>
+      <c r="L80" s="20">
+        <v>252243</v>
+      </c>
+    </row>
+    <row r="81" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A81" s="19" t="s">
+        <v>331</v>
+      </c>
+      <c r="B81" s="19" t="s">
+        <v>332</v>
+      </c>
+      <c r="C81" s="19" t="s">
+        <v>331</v>
+      </c>
+      <c r="D81" s="20"/>
+      <c r="E81" s="20"/>
+      <c r="F81" s="20"/>
+      <c r="G81" s="20"/>
+      <c r="H81" s="20"/>
+      <c r="I81" s="20"/>
+      <c r="J81" s="20">
+        <v>25000</v>
+      </c>
+      <c r="K81" s="20"/>
+      <c r="L81" s="20">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="82" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A82" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="B82" s="19" t="s">
+        <v>334</v>
+      </c>
+      <c r="C82" s="19" t="s">
+        <v>335</v>
+      </c>
+      <c r="D82" s="20"/>
+      <c r="E82" s="20"/>
+      <c r="F82" s="20"/>
+      <c r="G82" s="20"/>
+      <c r="H82" s="20"/>
+      <c r="I82" s="20"/>
+      <c r="J82" s="20">
+        <v>20000</v>
+      </c>
+      <c r="K82" s="20"/>
+      <c r="L82" s="20">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="83" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A83" s="19" t="s">
+        <v>336</v>
+      </c>
+      <c r="B83" s="19" t="s">
+        <v>337</v>
+      </c>
+      <c r="C83" s="19" t="s">
+        <v>338</v>
+      </c>
+      <c r="D83" s="20"/>
+      <c r="E83" s="20"/>
+      <c r="F83" s="20"/>
+      <c r="G83" s="20"/>
+      <c r="H83" s="20"/>
+      <c r="I83" s="20"/>
+      <c r="J83" s="20">
+        <v>50000</v>
+      </c>
+      <c r="K83" s="20"/>
+      <c r="L83" s="20">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="84" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A84" s="19" t="s">
+        <v>339</v>
+      </c>
+      <c r="B84" s="19" t="s">
+        <v>340</v>
+      </c>
+      <c r="C84" s="19" t="s">
+        <v>341</v>
+      </c>
+      <c r="D84" s="20"/>
+      <c r="E84" s="20"/>
+      <c r="F84" s="20"/>
+      <c r="G84" s="20"/>
+      <c r="H84" s="20"/>
+      <c r="I84" s="20"/>
+      <c r="J84" s="20">
+        <v>50000</v>
+      </c>
+      <c r="K84" s="20"/>
+      <c r="L84" s="20">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="85" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A85" s="19" t="s">
+        <v>342</v>
+      </c>
+      <c r="B85" s="19" t="s">
+        <v>343</v>
+      </c>
+      <c r="C85" s="19" t="s">
+        <v>344</v>
+      </c>
+      <c r="D85" s="20"/>
+      <c r="E85" s="20"/>
+      <c r="F85" s="20"/>
+      <c r="G85" s="20"/>
+      <c r="H85" s="20"/>
+      <c r="I85" s="20"/>
+      <c r="J85" s="20">
+        <v>20000</v>
+      </c>
+      <c r="K85" s="20"/>
+      <c r="L85" s="20">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="86" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A86" s="19" t="s">
+        <v>345</v>
+      </c>
+      <c r="B86" s="19" t="s">
+        <v>334</v>
+      </c>
+      <c r="C86" s="19" t="s">
+        <v>346</v>
+      </c>
+      <c r="D86" s="20"/>
+      <c r="E86" s="20"/>
+      <c r="F86" s="20"/>
+      <c r="G86" s="20"/>
+      <c r="H86" s="20"/>
+      <c r="I86" s="20"/>
+      <c r="J86" s="20">
+        <v>25000</v>
+      </c>
+      <c r="K86" s="20"/>
+      <c r="L86" s="20">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="87" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A87" s="19" t="s">
+        <v>347</v>
+      </c>
+      <c r="B87" s="19" t="s">
+        <v>348</v>
+      </c>
+      <c r="C87" s="19" t="s">
+        <v>347</v>
+      </c>
+      <c r="D87" s="20"/>
+      <c r="E87" s="20"/>
+      <c r="F87" s="20"/>
+      <c r="G87" s="20"/>
+      <c r="H87" s="20"/>
+      <c r="I87" s="20"/>
+      <c r="J87" s="20">
+        <v>10000</v>
+      </c>
+      <c r="K87" s="20"/>
+      <c r="L87" s="20">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="88" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A88" s="19" t="s">
+        <v>349</v>
+      </c>
+      <c r="B88" s="19" t="s">
+        <v>334</v>
+      </c>
+      <c r="C88" s="19" t="s">
+        <v>349</v>
+      </c>
+      <c r="D88" s="20"/>
+      <c r="E88" s="20"/>
+      <c r="F88" s="20"/>
+      <c r="G88" s="20"/>
+      <c r="H88" s="20"/>
+      <c r="I88" s="20"/>
+      <c r="J88" s="20">
+        <v>100000</v>
+      </c>
+      <c r="K88" s="20"/>
+      <c r="L88" s="20">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="89" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A89" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="B89" s="19" t="s">
+        <v>337</v>
+      </c>
+      <c r="C89" s="19" t="s">
+        <v>338</v>
+      </c>
+      <c r="D89" s="20"/>
+      <c r="E89" s="20"/>
+      <c r="F89" s="20"/>
+      <c r="G89" s="20"/>
+      <c r="H89" s="20"/>
+      <c r="I89" s="20"/>
+      <c r="J89" s="20">
+        <v>20000</v>
+      </c>
+      <c r="K89" s="20"/>
+      <c r="L89" s="20">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="90" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A90" s="19" t="s">
+        <v>351</v>
+      </c>
+      <c r="B90" s="19" t="s">
+        <v>352</v>
+      </c>
+      <c r="C90" s="19" t="s">
+        <v>353</v>
+      </c>
+      <c r="D90" s="20"/>
+      <c r="E90" s="20"/>
+      <c r="F90" s="20"/>
+      <c r="G90" s="20"/>
+      <c r="H90" s="20"/>
+      <c r="I90" s="20"/>
+      <c r="J90" s="20">
+        <v>25000</v>
+      </c>
+      <c r="K90" s="20"/>
+      <c r="L90" s="20">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="91" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A91" s="19" t="s">
+        <v>354</v>
+      </c>
+      <c r="B91" s="19" t="s">
+        <v>355</v>
+      </c>
+      <c r="C91" s="19" t="s">
+        <v>354</v>
+      </c>
+      <c r="D91" s="20"/>
+      <c r="E91" s="20"/>
+      <c r="F91" s="20"/>
+      <c r="G91" s="20"/>
+      <c r="H91" s="20"/>
+      <c r="I91" s="20"/>
+      <c r="J91" s="20"/>
+      <c r="K91" s="20">
+        <v>100000</v>
+      </c>
+      <c r="L91" s="20">
+        <v>-100000</v>
+      </c>
+    </row>
+    <row r="92" ht="14" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A92" s="19" t="s">
+        <v>356</v>
+      </c>
+      <c r="B92" s="19" t="s">
+        <v>357</v>
+      </c>
+      <c r="C92" s="19" t="s">
+        <v>356</v>
+      </c>
+      <c r="D92" s="20"/>
+      <c r="E92" s="20"/>
+      <c r="F92" s="20"/>
+      <c r="G92" s="20"/>
+      <c r="H92" s="20"/>
+      <c r="I92" s="20"/>
+      <c r="J92" s="20"/>
+      <c r="K92" s="20">
+        <v>50000</v>
+      </c>
+      <c r="L92" s="20">
+        <v>-50000</v>
       </c>
     </row>
   </sheetData>
@@ -5900,7 +7931,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
-        <v>241</v>
+        <v>101</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21"/>
@@ -5910,7 +7941,7 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>242</v>
+        <v>358</v>
       </c>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
@@ -5920,7 +7951,7 @@
     </row>
     <row r="3" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
-        <v>243</v>
+        <v>359</v>
       </c>
       <c r="B3" s="23"/>
       <c r="C3" s="23"/>
@@ -5930,7 +7961,7 @@
     </row>
     <row r="4" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>244</v>
+        <v>360</v>
       </c>
       <c r="B4" s="24"/>
       <c r="C4" s="24"/>
@@ -5940,13 +7971,13 @@
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="25" t="s">
-        <v>245</v>
+        <v>361</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>246</v>
+        <v>362</v>
       </c>
       <c r="D5" s="26" t="s">
         <v>48</v>
@@ -5954,7 +7985,7 @@
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="27" t="s">
-        <v>247</v>
+        <v>363</v>
       </c>
       <c r="B6" s="27"/>
       <c r="C6" s="27"/>
@@ -5962,59 +7993,63 @@
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
-        <v>248</v>
+        <v>364</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>249</v>
+        <v>365</v>
       </c>
       <c r="C7" s="20">
-        <v>3050000</v>
+        <v>51217493</v>
       </c>
       <c r="D7" s="20"/>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>250</v>
+        <v>366</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>251</v>
-      </c>
-      <c r="C8" s="20"/>
+        <v>367</v>
+      </c>
+      <c r="C8" s="20">
+        <v>1700000</v>
+      </c>
       <c r="D8" s="20"/>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>252</v>
+        <v>368</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>253</v>
-      </c>
-      <c r="C9" s="20"/>
+        <v>369</v>
+      </c>
+      <c r="C9" s="20">
+        <v>275000</v>
+      </c>
       <c r="D9" s="20"/>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>254</v>
+        <v>370</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>255</v>
+        <v>371</v>
       </c>
       <c r="C10" s="20"/>
       <c r="D10" s="20"/>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="29" t="s">
-        <v>256</v>
+        <v>372</v>
       </c>
       <c r="B11" s="29"/>
       <c r="C11" s="30">
-        <v>3050000</v>
+        <v>53192493</v>
       </c>
       <c r="D11" s="30"/>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="27" t="s">
-        <v>257</v>
+        <v>373</v>
       </c>
       <c r="B12" s="27"/>
       <c r="C12" s="27"/>
@@ -6022,77 +8057,75 @@
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>258</v>
+        <v>374</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>251</v>
+        <v>367</v>
       </c>
       <c r="C13" s="20"/>
       <c r="D13" s="20"/>
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
-        <v>259</v>
+        <v>375</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>260</v>
+        <v>376</v>
       </c>
       <c r="C14" s="20">
-        <v>320000</v>
+        <v>2825000</v>
       </c>
       <c r="D14" s="20"/>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>261</v>
+        <v>377</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>262</v>
+        <v>378</v>
       </c>
       <c r="C15" s="20">
-        <v>335000</v>
+        <v>1427000</v>
       </c>
       <c r="D15" s="20"/>
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>263</v>
+        <v>379</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>264</v>
-      </c>
-      <c r="C16" s="20">
-        <v>800000</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="C16" s="20"/>
       <c r="D16" s="20"/>
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
-        <v>265</v>
+        <v>381</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>266</v>
+        <v>382</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="20"/>
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="29" t="s">
-        <v>267</v>
+        <v>383</v>
       </c>
       <c r="B18" s="29"/>
       <c r="C18" s="30">
-        <v>1455000</v>
+        <v>4252000</v>
       </c>
       <c r="D18" s="30"/>
     </row>
     <row r="19" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
-        <v>268</v>
+        <v>384</v>
       </c>
       <c r="B19" s="31"/>
       <c r="C19" s="32">
-        <v>4505000</v>
+        <v>57444493</v>
       </c>
       <c r="D19" s="32"/>
     </row>
@@ -6107,51 +8140,51 @@
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
-        <v>269</v>
+        <v>385</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>270</v>
+        <v>386</v>
       </c>
       <c r="C21" s="20">
-        <v>2000000</v>
+        <v>51000000</v>
       </c>
       <c r="D21" s="20"/>
     </row>
     <row r="22" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
-        <v>271</v>
+        <v>387</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>272</v>
+        <v>388</v>
       </c>
       <c r="C22" s="20">
-        <v>500000</v>
+        <v>2532000</v>
       </c>
       <c r="D22" s="20"/>
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
-        <v>273</v>
+        <v>389</v>
       </c>
       <c r="B23" s="19"/>
       <c r="C23" s="20">
-        <v>749450</v>
+        <v>1634157</v>
       </c>
       <c r="D23" s="20"/>
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="29" t="s">
-        <v>274</v>
+        <v>390</v>
       </c>
       <c r="B24" s="29"/>
       <c r="C24" s="30">
-        <v>3249450</v>
+        <v>55166157</v>
       </c>
       <c r="D24" s="30"/>
     </row>
     <row r="25" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="27" t="s">
-        <v>275</v>
+        <v>391</v>
       </c>
       <c r="B25" s="27"/>
       <c r="C25" s="27"/>
@@ -6159,29 +8192,27 @@
     </row>
     <row r="26" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="19" t="s">
-        <v>276</v>
+        <v>392</v>
       </c>
       <c r="B26" s="28" t="s">
-        <v>277</v>
-      </c>
-      <c r="C26" s="20">
-        <v>800000</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="C26" s="20"/>
       <c r="D26" s="20"/>
     </row>
     <row r="27" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="19" t="s">
-        <v>278</v>
+        <v>394</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>279</v>
+        <v>395</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="20"/>
     </row>
     <row r="28" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="19" t="s">
-        <v>280</v>
+        <v>396</v>
       </c>
       <c r="B28" s="19"/>
       <c r="C28" s="20"/>
@@ -6189,17 +8220,15 @@
     </row>
     <row r="29" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="29" t="s">
-        <v>281</v>
+        <v>397</v>
       </c>
       <c r="B29" s="29"/>
-      <c r="C29" s="30">
-        <v>800000</v>
-      </c>
+      <c r="C29" s="30"/>
       <c r="D29" s="30"/>
     </row>
     <row r="30" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="27" t="s">
-        <v>282</v>
+        <v>398</v>
       </c>
       <c r="B30" s="27"/>
       <c r="C30" s="27"/>
@@ -6207,49 +8236,53 @@
     </row>
     <row r="31" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
-        <v>276</v>
+        <v>392</v>
       </c>
       <c r="B31" s="28" t="s">
-        <v>277</v>
-      </c>
-      <c r="C31" s="20"/>
+        <v>393</v>
+      </c>
+      <c r="C31" s="20">
+        <v>150000</v>
+      </c>
       <c r="D31" s="20"/>
     </row>
     <row r="32" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
-        <v>283</v>
+        <v>399</v>
       </c>
       <c r="B32" s="28" t="s">
-        <v>284</v>
+        <v>400</v>
       </c>
       <c r="C32" s="20">
-        <v>394500</v>
+        <v>865000</v>
       </c>
       <c r="D32" s="20"/>
     </row>
     <row r="33" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>285</v>
+        <v>401</v>
       </c>
       <c r="B33" s="19"/>
-      <c r="C33" s="20"/>
+      <c r="C33" s="20">
+        <v>479486</v>
+      </c>
       <c r="D33" s="20"/>
     </row>
     <row r="34" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="19" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="B34" s="28" t="s">
-        <v>279</v>
+        <v>395</v>
       </c>
       <c r="C34" s="20">
-        <v>61050</v>
+        <v>516949</v>
       </c>
       <c r="D34" s="20"/>
     </row>
     <row r="35" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>287</v>
+        <v>403</v>
       </c>
       <c r="B35" s="19"/>
       <c r="C35" s="20"/>
@@ -6257,27 +8290,27 @@
     </row>
     <row r="36" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="29" t="s">
-        <v>288</v>
+        <v>404</v>
       </c>
       <c r="B36" s="29"/>
       <c r="C36" s="30">
-        <v>455550</v>
+        <v>2011435</v>
       </c>
       <c r="D36" s="30"/>
     </row>
     <row r="37" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="31" t="s">
-        <v>289</v>
+        <v>405</v>
       </c>
       <c r="B37" s="31"/>
       <c r="C37" s="32">
-        <v>4505000</v>
+        <v>57177592</v>
       </c>
       <c r="D37" s="32"/>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="34" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="C38" s="35">
         <f>=C25-C37</f>
@@ -6285,12 +8318,12 @@
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="34" t="s">
-        <v>291</v>
+        <v>407</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="36" t="s">
-        <v>292</v>
+        <v>408</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -6302,65 +8335,65 @@
     </row>
     <row r="44" ht="12" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="38" t="s">
-        <v>293</v>
+        <v>409</v>
       </c>
     </row>
     <row r="45" ht="12" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="39" t="s">
-        <v>151</v>
+        <v>410</v>
       </c>
       <c r="C45" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="46" ht="12" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="38" t="s">
-        <v>294</v>
+        <v>411</v>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="40" t="s">
-        <v>295</v>
+        <v>412</v>
       </c>
     </row>
     <row r="48" ht="12" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="39" t="s">
-        <v>151</v>
+        <v>410</v>
       </c>
     </row>
     <row r="49" ht="12" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="38" t="s">
-        <v>296</v>
+        <v>413</v>
       </c>
     </row>
     <row r="50" ht="33" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="40" t="s">
-        <v>297</v>
+        <v>414</v>
       </c>
     </row>
     <row r="51" ht="12" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="39" t="s">
-        <v>151</v>
+        <v>410</v>
       </c>
     </row>
     <row r="52" ht="12" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="38" t="s">
-        <v>298</v>
+        <v>415</v>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="40" t="s">
-        <v>299</v>
+        <v>416</v>
       </c>
     </row>
     <row r="54" ht="12" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="39" t="s">
-        <v>151</v>
+        <v>410</v>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="41" t="s">
-        <v>300</v>
+        <v>417</v>
       </c>
     </row>
   </sheetData>
@@ -6378,7 +8411,7 @@
   </mergeCells>
   <pageSetup paperSize="9" orientation="portrait" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;CHimalayan Trading Pvt. Ltd.</oddHeader>
+    <oddHeader>&amp;CABC PRIVATE LIMITED</oddHeader>
     <oddFooter>&amp;CPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
@@ -6400,7 +8433,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
-        <v>241</v>
+        <v>101</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21"/>
@@ -6410,7 +8443,7 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>301</v>
+        <v>418</v>
       </c>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
@@ -6420,7 +8453,7 @@
     </row>
     <row r="3" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
-        <v>302</v>
+        <v>419</v>
       </c>
       <c r="B3" s="23"/>
       <c r="C3" s="23"/>
@@ -6430,7 +8463,7 @@
     </row>
     <row r="4" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>244</v>
+        <v>360</v>
       </c>
       <c r="B4" s="24"/>
       <c r="C4" s="24"/>
@@ -6440,21 +8473,21 @@
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="25" t="s">
-        <v>245</v>
+        <v>361</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C5" s="26" t="s">
         <v>51</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>303</v>
+        <v>420</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="27" t="s">
-        <v>304</v>
+        <v>421</v>
       </c>
       <c r="B6" s="27"/>
       <c r="C6" s="27"/>
@@ -6462,45 +8495,49 @@
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
-        <v>305</v>
+        <v>422</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>306</v>
+        <v>423</v>
       </c>
       <c r="C7" s="20">
-        <v>3500000</v>
+        <v>10500000</v>
       </c>
       <c r="D7" s="20"/>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>307</v>
+        <v>424</v>
       </c>
       <c r="B8" s="19"/>
-      <c r="C8" s="20"/>
+      <c r="C8" s="20">
+        <v>2000</v>
+      </c>
       <c r="D8" s="20"/>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>308</v>
+        <v>425</v>
       </c>
       <c r="B9" s="19"/>
-      <c r="C9" s="20"/>
+      <c r="C9" s="20">
+        <v>70000</v>
+      </c>
       <c r="D9" s="20"/>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="29" t="s">
-        <v>309</v>
+        <v>426</v>
       </c>
       <c r="B10" s="29"/>
       <c r="C10" s="30">
-        <v>3500000</v>
+        <v>10572000</v>
       </c>
       <c r="D10" s="30"/>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="27" t="s">
-        <v>310</v>
+        <v>427</v>
       </c>
       <c r="B11" s="27"/>
       <c r="C11" s="27"/>
@@ -6508,54 +8545,56 @@
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>311</v>
+        <v>428</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>312</v>
+        <v>429</v>
       </c>
       <c r="C12" s="20">
-        <v>1780000</v>
+        <v>6000000</v>
       </c>
       <c r="D12" s="20"/>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>313</v>
+        <v>430</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>314</v>
-      </c>
-      <c r="C13" s="20"/>
+        <v>431</v>
+      </c>
+      <c r="C13" s="20">
+        <v>600000</v>
+      </c>
       <c r="D13" s="20"/>
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
-        <v>315</v>
+        <v>432</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>316</v>
+        <v>433</v>
       </c>
       <c r="C14" s="20">
-        <v>305200</v>
+        <v>770000</v>
       </c>
       <c r="D14" s="20"/>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>317</v>
+        <v>434</v>
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="20">
-        <v>72000</v>
+        <v>260000</v>
       </c>
       <c r="D15" s="20"/>
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>318</v>
+        <v>435</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>249</v>
+        <v>365</v>
       </c>
       <c r="C16" s="20">
         <v>150000</v>
@@ -6564,94 +8603,98 @@
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
-        <v>319</v>
+        <v>436</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>320</v>
-      </c>
-      <c r="C17" s="20"/>
+        <v>437</v>
+      </c>
+      <c r="C17" s="20">
+        <v>300000</v>
+      </c>
       <c r="D17" s="20"/>
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
-        <v>321</v>
+        <v>438</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>322</v>
+        <v>439</v>
       </c>
       <c r="C18" s="20">
-        <v>582300</v>
+        <v>396000</v>
       </c>
       <c r="D18" s="20"/>
     </row>
     <row r="19" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="29" t="s">
-        <v>323</v>
+        <v>440</v>
       </c>
       <c r="B19" s="29"/>
       <c r="C19" s="30">
-        <v>2889500</v>
+        <v>8476000</v>
       </c>
       <c r="D19" s="30"/>
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="29" t="s">
-        <v>324</v>
+        <v>441</v>
       </c>
       <c r="B20" s="29"/>
       <c r="C20" s="30">
-        <v>610500</v>
+        <v>2096000</v>
       </c>
       <c r="D20" s="30"/>
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
-        <v>325</v>
+        <v>442</v>
       </c>
       <c r="B21" s="19"/>
       <c r="C21" s="20">
-        <v>61050</v>
+        <v>209600</v>
       </c>
       <c r="D21" s="20"/>
     </row>
     <row r="22" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="29" t="s">
-        <v>326</v>
+        <v>443</v>
       </c>
       <c r="B22" s="29"/>
       <c r="C22" s="30">
-        <v>549450</v>
+        <v>1886400</v>
       </c>
       <c r="D22" s="30"/>
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
-        <v>327</v>
+        <v>444</v>
       </c>
       <c r="B23" s="28" t="s">
-        <v>328</v>
-      </c>
-      <c r="C23" s="20"/>
+        <v>445</v>
+      </c>
+      <c r="C23" s="20">
+        <v>252243</v>
+      </c>
       <c r="D23" s="20"/>
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="31" t="s">
-        <v>329</v>
+        <v>446</v>
       </c>
       <c r="B24" s="31"/>
       <c r="C24" s="32">
-        <v>549450</v>
+        <v>1634157</v>
       </c>
       <c r="D24" s="32"/>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="34" t="s">
-        <v>291</v>
+        <v>407</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="36" t="s">
-        <v>292</v>
+        <v>408</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -6663,65 +8706,65 @@
     </row>
     <row r="30" ht="12" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="38" t="s">
-        <v>293</v>
+        <v>409</v>
       </c>
     </row>
     <row r="31" ht="12" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="39" t="s">
-        <v>151</v>
+        <v>410</v>
       </c>
       <c r="C31" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="32" ht="12" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="38" t="s">
-        <v>294</v>
+        <v>411</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="40" t="s">
-        <v>295</v>
+        <v>412</v>
       </c>
     </row>
     <row r="34" ht="12" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="39" t="s">
-        <v>151</v>
+        <v>410</v>
       </c>
     </row>
     <row r="35" ht="12" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="38" t="s">
-        <v>296</v>
+        <v>413</v>
       </c>
     </row>
     <row r="36" ht="33" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="40" t="s">
-        <v>297</v>
+        <v>414</v>
       </c>
     </row>
     <row r="37" ht="12" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="39" t="s">
-        <v>151</v>
+        <v>410</v>
       </c>
     </row>
     <row r="38" ht="12" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="38" t="s">
-        <v>298</v>
+        <v>415</v>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="40" t="s">
-        <v>299</v>
+        <v>416</v>
       </c>
     </row>
     <row r="40" ht="12" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="39" t="s">
-        <v>151</v>
+        <v>410</v>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="41" t="s">
-        <v>300</v>
+        <v>417</v>
       </c>
     </row>
   </sheetData>
@@ -6736,7 +8779,7 @@
   </mergeCells>
   <pageSetup paperSize="9" orientation="portrait" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;CHimalayan Trading Pvt. Ltd.</oddHeader>
+    <oddHeader>&amp;CABC PRIVATE LIMITED</oddHeader>
     <oddFooter>&amp;CPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
@@ -6760,7 +8803,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="42" t="s">
-        <v>241</v>
+        <v>101</v>
       </c>
       <c r="B1" s="42"/>
       <c r="C1" s="42"/>
@@ -6770,7 +8813,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="43" t="s">
-        <v>330</v>
+        <v>447</v>
       </c>
       <c r="B2" s="43"/>
       <c r="C2" s="43"/>
@@ -6780,7 +8823,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="44" t="s">
-        <v>302</v>
+        <v>419</v>
       </c>
       <c r="B3" s="44"/>
       <c r="C3" s="44"/>
@@ -6790,65 +8833,71 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="45" t="s">
-        <v>245</v>
+        <v>361</v>
       </c>
       <c r="B5" s="46" t="s">
-        <v>331</v>
+        <v>448</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>332</v>
+        <v>449</v>
       </c>
       <c r="D5" s="46" t="s">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="E5" s="46" t="s">
-        <v>212</v>
+        <v>450</v>
       </c>
       <c r="F5" s="46" t="s">
-        <v>333</v>
+        <v>451</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>334</v>
-      </c>
-      <c r="B6" s="20"/>
+        <v>452</v>
+      </c>
+      <c r="B6" s="20">
+        <v>50000000</v>
+      </c>
       <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
+      <c r="D6" s="20">
+        <v>2532000</v>
+      </c>
       <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
+      <c r="F6" s="20">
+        <v>52532000</v>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
-        <v>335</v>
+        <v>453</v>
       </c>
       <c r="B7" s="20"/>
       <c r="C7" s="20"/>
       <c r="D7" s="20"/>
       <c r="E7" s="20">
-        <v>549450</v>
+        <v>1634157</v>
       </c>
       <c r="F7" s="20">
-        <v>549450</v>
+        <v>1634157</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>336</v>
+        <v>454</v>
       </c>
       <c r="B8" s="20">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
       <c r="C8" s="20"/>
       <c r="D8" s="20"/>
       <c r="E8" s="20"/>
       <c r="F8" s="20">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>337</v>
+        <v>455</v>
       </c>
       <c r="B9" s="20"/>
       <c r="C9" s="20"/>
@@ -6858,7 +8907,7 @@
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>338</v>
+        <v>456</v>
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="20"/>
@@ -6868,20 +8917,20 @@
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="47" t="s">
-        <v>339</v>
+        <v>457</v>
       </c>
       <c r="B11" s="48">
-        <v>2000000</v>
+        <v>51000000</v>
       </c>
       <c r="C11" s="48"/>
       <c r="D11" s="48">
-        <v>500000</v>
+        <v>2532000</v>
       </c>
       <c r="E11" s="48">
-        <v>549450</v>
+        <v>1634157</v>
       </c>
       <c r="F11" s="48">
-        <v>3049450</v>
+        <v>55166157</v>
       </c>
     </row>
   </sheetData>
@@ -6910,7 +8959,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
-        <v>241</v>
+        <v>101</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21"/>
@@ -6920,7 +8969,7 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>340</v>
+        <v>458</v>
       </c>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
@@ -6930,7 +8979,7 @@
     </row>
     <row r="3" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
-        <v>302</v>
+        <v>419</v>
       </c>
       <c r="B3" s="23"/>
       <c r="C3" s="23"/>
@@ -6940,7 +8989,7 @@
     </row>
     <row r="4" ht="14" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>244</v>
+        <v>360</v>
       </c>
       <c r="B4" s="24"/>
       <c r="C4" s="24"/>
@@ -6950,21 +8999,21 @@
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="25" t="s">
-        <v>245</v>
+        <v>361</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C5" s="26" t="s">
         <v>51</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>151</v>
+        <v>410</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="27" t="s">
-        <v>341</v>
+        <v>459</v>
       </c>
       <c r="B6" s="27"/>
       <c r="C6" s="27"/>
@@ -6972,17 +9021,17 @@
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
-        <v>342</v>
+        <v>460</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="20">
-        <v>549450</v>
+        <v>1886400</v>
       </c>
       <c r="D7" s="20"/>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>343</v>
+        <v>461</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="20"/>
@@ -6990,7 +9039,7 @@
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>344</v>
+        <v>462</v>
       </c>
       <c r="B9" s="19"/>
       <c r="C9" s="20">
@@ -7000,41 +9049,47 @@
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>345</v>
+        <v>463</v>
       </c>
       <c r="B10" s="19"/>
-      <c r="C10" s="20"/>
+      <c r="C10" s="20">
+        <v>300000</v>
+      </c>
       <c r="D10" s="20"/>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>346</v>
+        <v>464</v>
       </c>
       <c r="B11" s="19"/>
-      <c r="C11" s="20"/>
+      <c r="C11" s="20">
+        <v>-2000</v>
+      </c>
       <c r="D11" s="20"/>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>347</v>
+        <v>465</v>
       </c>
       <c r="B12" s="19"/>
-      <c r="C12" s="20"/>
+      <c r="C12" s="20">
+        <v>-10000</v>
+      </c>
       <c r="D12" s="20"/>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>348</v>
+        <v>466</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="20">
-        <v>72000</v>
+        <v>260000</v>
       </c>
       <c r="D13" s="20"/>
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
-        <v>349</v>
+        <v>467</v>
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="20"/>
@@ -7042,7 +9097,7 @@
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>350</v>
+        <v>468</v>
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="20"/>
@@ -7050,7 +9105,7 @@
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>351</v>
+        <v>469</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="20"/>
@@ -7058,27 +9113,25 @@
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
-        <v>352</v>
+        <v>470</v>
       </c>
       <c r="B17" s="19"/>
       <c r="C17" s="20">
-        <v>-335000</v>
+        <v>45000</v>
       </c>
       <c r="D17" s="20"/>
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
-        <v>353</v>
+        <v>471</v>
       </c>
       <c r="B18" s="19"/>
-      <c r="C18" s="20">
-        <v>-320000</v>
-      </c>
+      <c r="C18" s="20"/>
       <c r="D18" s="20"/>
     </row>
     <row r="19" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>354</v>
+        <v>472</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="20"/>
@@ -7086,71 +9139,77 @@
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
-        <v>355</v>
+        <v>473</v>
       </c>
       <c r="B20" s="19"/>
       <c r="C20" s="20">
-        <v>394500</v>
+        <v>475000</v>
       </c>
       <c r="D20" s="20"/>
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
-        <v>356</v>
+        <v>474</v>
       </c>
       <c r="B21" s="19"/>
-      <c r="C21" s="20"/>
+      <c r="C21" s="20">
+        <v>424486</v>
+      </c>
       <c r="D21" s="20"/>
     </row>
     <row r="22" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
-        <v>357</v>
+        <v>475</v>
       </c>
       <c r="B22" s="19"/>
-      <c r="C22" s="20"/>
+      <c r="C22" s="20">
+        <v>167349</v>
+      </c>
       <c r="D22" s="20"/>
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="29" t="s">
-        <v>358</v>
+        <v>476</v>
       </c>
       <c r="B23" s="29"/>
       <c r="C23" s="30">
-        <v>510950</v>
+        <v>3696235</v>
       </c>
       <c r="D23" s="30"/>
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
-        <v>359</v>
+        <v>477</v>
       </c>
       <c r="B24" s="19"/>
       <c r="C24" s="20">
-        <v>-72000</v>
+        <v>-260000</v>
       </c>
       <c r="D24" s="20"/>
     </row>
     <row r="25" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="19" t="s">
-        <v>360</v>
+        <v>478</v>
       </c>
       <c r="B25" s="19"/>
-      <c r="C25" s="20"/>
+      <c r="C25" s="20">
+        <v>-252243</v>
+      </c>
       <c r="D25" s="20"/>
     </row>
     <row r="26" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="29" t="s">
-        <v>361</v>
+        <v>479</v>
       </c>
       <c r="B26" s="29"/>
       <c r="C26" s="30">
-        <v>438950</v>
+        <v>3183992</v>
       </c>
       <c r="D26" s="30"/>
     </row>
     <row r="27" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="27" t="s">
-        <v>362</v>
+        <v>480</v>
       </c>
       <c r="B27" s="27"/>
       <c r="C27" s="27"/>
@@ -7158,7 +9217,7 @@
     </row>
     <row r="28" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="19" t="s">
-        <v>363</v>
+        <v>481</v>
       </c>
       <c r="B28" s="19"/>
       <c r="C28" s="20"/>
@@ -7166,23 +9225,27 @@
     </row>
     <row r="29" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
-        <v>364</v>
+        <v>482</v>
       </c>
       <c r="B29" s="19"/>
-      <c r="C29" s="20"/>
+      <c r="C29" s="20">
+        <v>2000</v>
+      </c>
       <c r="D29" s="20"/>
     </row>
     <row r="30" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
-        <v>365</v>
+        <v>483</v>
       </c>
       <c r="B30" s="19"/>
-      <c r="C30" s="20"/>
+      <c r="C30" s="20">
+        <v>10000</v>
+      </c>
       <c r="D30" s="20"/>
     </row>
     <row r="31" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
-        <v>366</v>
+        <v>484</v>
       </c>
       <c r="B31" s="19"/>
       <c r="C31" s="20"/>
@@ -7190,23 +9253,27 @@
     </row>
     <row r="32" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
-        <v>367</v>
+        <v>485</v>
       </c>
       <c r="B32" s="19"/>
-      <c r="C32" s="20"/>
+      <c r="C32" s="20">
+        <v>-1700000</v>
+      </c>
       <c r="D32" s="20"/>
     </row>
     <row r="33" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="29" t="s">
-        <v>368</v>
+        <v>486</v>
       </c>
       <c r="B33" s="29"/>
-      <c r="C33" s="30"/>
+      <c r="C33" s="30">
+        <v>-1688000</v>
+      </c>
       <c r="D33" s="30"/>
     </row>
     <row r="34" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="27" t="s">
-        <v>369</v>
+        <v>487</v>
       </c>
       <c r="B34" s="27"/>
       <c r="C34" s="27"/>
@@ -7214,27 +9281,25 @@
     </row>
     <row r="35" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>370</v>
+        <v>488</v>
       </c>
       <c r="B35" s="19"/>
       <c r="C35" s="20">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
       <c r="D35" s="20"/>
     </row>
     <row r="36" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>371</v>
+        <v>489</v>
       </c>
       <c r="B36" s="19"/>
-      <c r="C36" s="20">
-        <v>800000</v>
-      </c>
+      <c r="C36" s="20"/>
       <c r="D36" s="20"/>
     </row>
     <row r="37" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>372</v>
+        <v>490</v>
       </c>
       <c r="B37" s="19"/>
       <c r="C37" s="20"/>
@@ -7242,15 +9307,17 @@
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
-        <v>373</v>
+        <v>491</v>
       </c>
       <c r="B38" s="19"/>
-      <c r="C38" s="20"/>
+      <c r="C38" s="20">
+        <v>150000</v>
+      </c>
       <c r="D38" s="20"/>
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
-        <v>374</v>
+        <v>492</v>
       </c>
       <c r="B39" s="19"/>
       <c r="C39" s="20"/>
@@ -7258,7 +9325,7 @@
     </row>
     <row r="40" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
-        <v>375</v>
+        <v>493</v>
       </c>
       <c r="B40" s="19"/>
       <c r="C40" s="20"/>
@@ -7266,27 +9333,27 @@
     </row>
     <row r="41" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="29" t="s">
-        <v>376</v>
+        <v>494</v>
       </c>
       <c r="B41" s="29"/>
       <c r="C41" s="30">
-        <v>2800000</v>
+        <v>1150000</v>
       </c>
       <c r="D41" s="30"/>
     </row>
     <row r="42" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="31" t="s">
-        <v>377</v>
+        <v>495</v>
       </c>
       <c r="B42" s="31"/>
       <c r="C42" s="32">
-        <v>3238950</v>
+        <v>2645992</v>
       </c>
       <c r="D42" s="32"/>
     </row>
     <row r="43" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="19" t="s">
-        <v>378</v>
+        <v>496</v>
       </c>
       <c r="B43" s="19"/>
       <c r="C43" s="49">
@@ -7297,55 +9364,53 @@
     </row>
     <row r="44" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="29" t="s">
-        <v>379</v>
+        <v>497</v>
       </c>
       <c r="B44" s="29"/>
-      <c r="C44" s="30">
-        <v>800000</v>
-      </c>
+      <c r="C44" s="30"/>
       <c r="D44" s="30"/>
     </row>
     <row r="45" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="19" t="s">
-        <v>380</v>
+        <v>498</v>
       </c>
       <c r="B45" s="19"/>
       <c r="C45" s="20">
-        <v>-2438950</v>
+        <v>844008</v>
       </c>
       <c r="D45" s="20"/>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="34" t="s">
-        <v>291</v>
+        <v>407</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="36" t="s">
-        <v>292</v>
+        <v>408</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C52" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>381</v>
+        <v>499</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>382</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -7381,205 +9446,205 @@
     </row>
     <row r="2" ht="15" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B2" s="51" t="s">
-        <v>383</v>
+        <v>501</v>
       </c>
     </row>
     <row r="3" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" s="50" t="s">
-        <v>384</v>
+        <v>502</v>
       </c>
     </row>
     <row r="5" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" ht="18" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B6" s="52" t="s">
-        <v>385</v>
+        <v>503</v>
       </c>
     </row>
     <row r="7" ht="70" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7" s="51" t="s">
-        <v>386</v>
+        <v>504</v>
       </c>
     </row>
     <row r="8" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" ht="18" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B9" s="52" t="s">
-        <v>387</v>
+        <v>505</v>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B10" s="51" t="s">
-        <v>388</v>
+        <v>506</v>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B11" s="51" t="s">
-        <v>389</v>
+        <v>507</v>
       </c>
     </row>
     <row r="12" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" ht="18" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B13" s="52" t="s">
-        <v>390</v>
+        <v>508</v>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B14" s="51" t="s">
-        <v>391</v>
+        <v>509</v>
       </c>
     </row>
     <row r="15" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="16" ht="18" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B16" s="52" t="s">
-        <v>392</v>
+        <v>510</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="51" t="s">
-        <v>393</v>
+        <v>511</v>
       </c>
     </row>
     <row r="18" ht="56" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="51" t="s">
-        <v>394</v>
+        <v>512</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" s="51" t="s">
-        <v>395</v>
+        <v>513</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" s="51" t="s">
-        <v>396</v>
+        <v>514</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" s="51" t="s">
-        <v>397</v>
+        <v>515</v>
       </c>
     </row>
     <row r="22" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" ht="18" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" s="52" t="s">
-        <v>398</v>
+        <v>516</v>
       </c>
     </row>
     <row r="24" ht="56" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" s="51" t="s">
-        <v>399</v>
+        <v>517</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" s="51" t="s">
-        <v>400</v>
+        <v>518</v>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" s="51" t="s">
-        <v>401</v>
+        <v>519</v>
       </c>
     </row>
     <row r="27" ht="56" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" s="51" t="s">
-        <v>402</v>
+        <v>520</v>
       </c>
     </row>
     <row r="28" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="29" ht="18" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" s="52" t="s">
-        <v>403</v>
+        <v>521</v>
       </c>
     </row>
     <row r="30" ht="42" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" s="51" t="s">
-        <v>404</v>
+        <v>522</v>
       </c>
     </row>
     <row r="31" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="32" ht="18" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B32" s="52" t="s">
-        <v>405</v>
+        <v>523</v>
       </c>
     </row>
     <row r="33" ht="42" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B33" s="51" t="s">
-        <v>406</v>
+        <v>524</v>
       </c>
     </row>
     <row r="34" ht="42" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B34" s="51" t="s">
-        <v>407</v>
+        <v>525</v>
       </c>
     </row>
     <row r="35" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="36" ht="18" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B36" s="52" t="s">
-        <v>408</v>
+        <v>526</v>
       </c>
     </row>
     <row r="37" ht="42" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B37" s="51" t="s">
-        <v>409</v>
+        <v>527</v>
       </c>
     </row>
     <row r="38" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="39" ht="18" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B39" s="52" t="s">
-        <v>410</v>
+        <v>528</v>
       </c>
     </row>
     <row r="40" ht="28" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B40" s="51" t="s">
-        <v>411</v>
+        <v>529</v>
       </c>
     </row>
     <row r="41" ht="28" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B41" s="51" t="s">
-        <v>412</v>
+        <v>530</v>
       </c>
     </row>
     <row r="42" ht="28" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B42" s="51" t="s">
-        <v>413</v>
+        <v>531</v>
       </c>
     </row>
     <row r="43" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="44" ht="18" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B44" s="52" t="s">
-        <v>414</v>
+        <v>532</v>
       </c>
     </row>
     <row r="45" ht="56" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B45" s="51" t="s">
-        <v>415</v>
+        <v>533</v>
       </c>
     </row>
     <row r="46" ht="56" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B46" s="51" t="s">
-        <v>416</v>
+        <v>534</v>
       </c>
     </row>
     <row r="47" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="48" ht="18" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B48" s="52" t="s">
-        <v>417</v>
+        <v>535</v>
       </c>
     </row>
     <row r="49" ht="84" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B49" s="51" t="s">
-        <v>418</v>
+        <v>536</v>
       </c>
     </row>
     <row r="50" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="51" ht="18" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B51" s="52" t="s">
-        <v>419</v>
+        <v>537</v>
       </c>
     </row>
     <row r="52" ht="28" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B52" s="51" t="s">
-        <v>420</v>
+        <v>538</v>
       </c>
     </row>
     <row r="53" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
